--- a/research/traditional_assets/database/data/croatia/croatia_household_products.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_household_products.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08592807841313593</v>
+        <v>0.0858103078719923</v>
       </c>
       <c r="C2">
-        <v>83.82666615091854</v>
+        <v>83.23319272780978</v>
       </c>
       <c r="D2">
-        <v>80.58666615091855</v>
+        <v>80.81419272780978</v>
       </c>
       <c r="E2">
-        <v>-18.3</v>
+        <v>-17.479</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.821</v>
       </c>
       <c r="G2">
         <v>3.24</v>
@@ -1439,28 +1439,28 @@
         <v>3.23</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04129629999999999</v>
       </c>
       <c r="N2">
-        <v>3.23</v>
+        <v>3.1887037</v>
       </c>
       <c r="O2">
-        <v>0.5814</v>
+        <v>0.573966666</v>
       </c>
       <c r="P2">
-        <v>2.648600000000001</v>
+        <v>2.614737034</v>
       </c>
       <c r="Q2">
-        <v>8.1586</v>
+        <v>8.124737034000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08592807841313593</v>
+        <v>0.08626045239595181</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6822213537559652</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>78.21523962195162</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0858103078719923</v>
+        <v>0.08569253733084865</v>
       </c>
       <c r="C3">
-        <v>83.23319272780978</v>
+        <v>82.64100772922788</v>
       </c>
       <c r="D3">
-        <v>80.81419272780978</v>
+        <v>81.04300772922788</v>
       </c>
       <c r="E3">
-        <v>-17.479</v>
+        <v>-16.658</v>
       </c>
       <c r="F3">
-        <v>0.821</v>
+        <v>1.642</v>
       </c>
       <c r="G3">
         <v>3.24</v>
@@ -1521,28 +1521,28 @@
         <v>3.23</v>
       </c>
       <c r="M3">
-        <v>0.04129629999999999</v>
+        <v>0.08259259999999999</v>
       </c>
       <c r="N3">
-        <v>3.1887037</v>
+        <v>3.147407400000001</v>
       </c>
       <c r="O3">
-        <v>0.573966666</v>
+        <v>0.5665333320000001</v>
       </c>
       <c r="P3">
-        <v>2.614737034</v>
+        <v>2.580874068</v>
       </c>
       <c r="Q3">
-        <v>8.124737034000001</v>
+        <v>8.090874068</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08626045239595181</v>
+        <v>0.08659960952127413</v>
       </c>
       <c r="T3">
-        <v>0.6822213537559652</v>
+        <v>0.6879400301293546</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>78.21523962195162</v>
+        <v>39.10761981097581</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08569253733084865</v>
+        <v>0.08557476678970501</v>
       </c>
       <c r="C4">
-        <v>82.64100772922788</v>
+        <v>82.05012213027285</v>
       </c>
       <c r="D4">
-        <v>81.04300772922788</v>
+        <v>81.27312213027285</v>
       </c>
       <c r="E4">
-        <v>-16.658</v>
+        <v>-15.837</v>
       </c>
       <c r="F4">
-        <v>1.642</v>
+        <v>2.463</v>
       </c>
       <c r="G4">
         <v>3.24</v>
@@ -1603,28 +1603,28 @@
         <v>3.23</v>
       </c>
       <c r="M4">
-        <v>0.08259259999999999</v>
+        <v>0.1238889</v>
       </c>
       <c r="N4">
-        <v>3.147407400000001</v>
+        <v>3.106111100000001</v>
       </c>
       <c r="O4">
-        <v>0.5665333320000001</v>
+        <v>0.5590999980000001</v>
       </c>
       <c r="P4">
-        <v>2.580874068</v>
+        <v>2.547011102</v>
       </c>
       <c r="Q4">
-        <v>8.090874068</v>
+        <v>8.057011102000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08659960952127413</v>
+        <v>0.08694575957701547</v>
       </c>
       <c r="T4">
-        <v>0.6879400301293546</v>
+        <v>0.6937766173558035</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>39.10761981097581</v>
+        <v>26.07174654065054</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08557476678970501</v>
+        <v>0.08545699624856135</v>
       </c>
       <c r="C5">
-        <v>82.05012213027285</v>
+        <v>81.46054703105091</v>
       </c>
       <c r="D5">
-        <v>81.27312213027285</v>
+        <v>81.50454703105092</v>
       </c>
       <c r="E5">
-        <v>-15.837</v>
+        <v>-15.016</v>
       </c>
       <c r="F5">
-        <v>2.463</v>
+        <v>3.284</v>
       </c>
       <c r="G5">
         <v>3.24</v>
@@ -1685,28 +1685,28 @@
         <v>3.23</v>
       </c>
       <c r="M5">
-        <v>0.1238889</v>
+        <v>0.1651852</v>
       </c>
       <c r="N5">
-        <v>3.106111100000001</v>
+        <v>3.064814800000001</v>
       </c>
       <c r="O5">
-        <v>0.5590999980000001</v>
+        <v>0.5516666640000001</v>
       </c>
       <c r="P5">
-        <v>2.547011102</v>
+        <v>2.513148136000001</v>
       </c>
       <c r="Q5">
-        <v>8.057011102000001</v>
+        <v>8.023148136</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08694575957701547</v>
+        <v>0.08729912109225141</v>
       </c>
       <c r="T5">
-        <v>0.6937766173558035</v>
+        <v>0.6997348001494701</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>26.07174654065054</v>
+        <v>19.55380990548791</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08545699624856135</v>
+        <v>0.08533922570741771</v>
       </c>
       <c r="C6">
-        <v>81.46054703105091</v>
+        <v>80.87229365845934</v>
       </c>
       <c r="D6">
-        <v>81.50454703105092</v>
+        <v>81.73729365845935</v>
       </c>
       <c r="E6">
-        <v>-15.016</v>
+        <v>-14.195</v>
       </c>
       <c r="F6">
-        <v>3.284</v>
+        <v>4.105</v>
       </c>
       <c r="G6">
         <v>3.24</v>
@@ -1767,28 +1767,28 @@
         <v>3.23</v>
       </c>
       <c r="M6">
-        <v>0.1651852</v>
+        <v>0.2064815</v>
       </c>
       <c r="N6">
-        <v>3.064814800000001</v>
+        <v>3.023518500000001</v>
       </c>
       <c r="O6">
-        <v>0.5516666640000001</v>
+        <v>0.5442333300000001</v>
       </c>
       <c r="P6">
-        <v>2.513148136000001</v>
+        <v>2.479285170000001</v>
       </c>
       <c r="Q6">
-        <v>8.023148136</v>
+        <v>7.98928517</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08729912109225141</v>
+        <v>0.0876599217972818</v>
       </c>
       <c r="T6">
-        <v>0.6997348001494701</v>
+        <v>0.7058184183703718</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.55380990548791</v>
+        <v>15.64304792439033</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08533922570741771</v>
+        <v>0.08522145516627407</v>
       </c>
       <c r="C7">
-        <v>80.87229365845934</v>
+        <v>80.28537336800207</v>
       </c>
       <c r="D7">
-        <v>81.73729365845935</v>
+        <v>81.97137336800208</v>
       </c>
       <c r="E7">
-        <v>-14.195</v>
+        <v>-13.374</v>
       </c>
       <c r="F7">
-        <v>4.105</v>
+        <v>4.926</v>
       </c>
       <c r="G7">
         <v>3.24</v>
@@ -1849,28 +1849,28 @@
         <v>3.23</v>
       </c>
       <c r="M7">
-        <v>0.2064815</v>
+        <v>0.2477778</v>
       </c>
       <c r="N7">
-        <v>3.023518500000001</v>
+        <v>2.9822222</v>
       </c>
       <c r="O7">
-        <v>0.5442333300000001</v>
+        <v>0.5367999960000001</v>
       </c>
       <c r="P7">
-        <v>2.479285170000001</v>
+        <v>2.445422204</v>
       </c>
       <c r="Q7">
-        <v>7.98928517</v>
+        <v>7.955422204</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0876599217972818</v>
+        <v>0.08802839911305751</v>
       </c>
       <c r="T7">
-        <v>0.7058184183703718</v>
+        <v>0.7120314752768246</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.64304792439033</v>
+        <v>13.03587327032527</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08522145516627407</v>
+        <v>0.08518978462513044</v>
       </c>
       <c r="C8">
-        <v>80.28537336800207</v>
+        <v>79.5275503872341</v>
       </c>
       <c r="D8">
-        <v>81.97137336800208</v>
+        <v>82.03455038723411</v>
       </c>
       <c r="E8">
-        <v>-13.374</v>
+        <v>-12.553</v>
       </c>
       <c r="F8">
-        <v>4.925999999999999</v>
+        <v>5.746999999999999</v>
       </c>
       <c r="G8">
         <v>3.24</v>
@@ -1931,45 +1931,45 @@
         <v>3.23</v>
       </c>
       <c r="M8">
-        <v>0.2477777999999999</v>
+        <v>0.2976945999999999</v>
       </c>
       <c r="N8">
-        <v>2.982222200000001</v>
+        <v>2.932305400000001</v>
       </c>
       <c r="O8">
-        <v>0.5367999960000001</v>
+        <v>0.527814972</v>
       </c>
       <c r="P8">
-        <v>2.445422204000001</v>
+        <v>2.404490428000001</v>
       </c>
       <c r="Q8">
-        <v>7.955422204</v>
+        <v>7.914490428000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08802839911305751</v>
+        <v>0.08840480067218326</v>
       </c>
       <c r="T8">
-        <v>0.7120314752768246</v>
+        <v>0.7183781463102979</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.18</v>
       </c>
       <c r="W8">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.03587327032527</v>
+        <v>10.85004565081127</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08518978462513042</v>
+        <v>0.08519583408398679</v>
       </c>
       <c r="C9">
-        <v>79.52755038723414</v>
+        <v>78.69447528449111</v>
       </c>
       <c r="D9">
-        <v>82.03455038723415</v>
+        <v>82.02247528449111</v>
       </c>
       <c r="E9">
-        <v>-12.553</v>
+        <v>-11.732</v>
       </c>
       <c r="F9">
-        <v>5.747</v>
+        <v>6.568</v>
       </c>
       <c r="G9">
         <v>3.24</v>
@@ -2013,45 +2013,45 @@
         <v>3.23</v>
       </c>
       <c r="M9">
-        <v>0.2976946</v>
+        <v>0.351388</v>
       </c>
       <c r="N9">
-        <v>2.932305400000001</v>
+        <v>2.878612</v>
       </c>
       <c r="O9">
-        <v>0.527814972</v>
+        <v>0.51815016</v>
       </c>
       <c r="P9">
-        <v>2.404490428000001</v>
+        <v>2.36046184</v>
       </c>
       <c r="Q9">
-        <v>7.914490428000001</v>
+        <v>7.87046184</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08840480067218326</v>
+        <v>0.08878938487389867</v>
       </c>
       <c r="T9">
-        <v>0.7183781463102979</v>
+        <v>0.7248627884531946</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.18</v>
       </c>
       <c r="W9">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.85004565081127</v>
+        <v>9.192118114448986</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08519583408398679</v>
+        <v>0.08510430354284315</v>
       </c>
       <c r="C10">
-        <v>78.69447528449111</v>
+        <v>78.05655688944178</v>
       </c>
       <c r="D10">
-        <v>82.02247528449111</v>
+        <v>82.20555688944178</v>
       </c>
       <c r="E10">
-        <v>-11.732</v>
+        <v>-10.911</v>
       </c>
       <c r="F10">
-        <v>6.568</v>
+        <v>7.388999999999999</v>
       </c>
       <c r="G10">
         <v>3.24</v>
@@ -2095,28 +2095,28 @@
         <v>3.23</v>
       </c>
       <c r="M10">
-        <v>0.351388</v>
+        <v>0.3953115</v>
       </c>
       <c r="N10">
-        <v>2.878612</v>
+        <v>2.8346885</v>
       </c>
       <c r="O10">
-        <v>0.51815016</v>
+        <v>0.51024393</v>
       </c>
       <c r="P10">
-        <v>2.36046184</v>
+        <v>2.32444457</v>
       </c>
       <c r="Q10">
-        <v>7.87046184</v>
+        <v>7.83444457</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08878938487389867</v>
+        <v>0.08918242147565181</v>
       </c>
       <c r="T10">
-        <v>0.7248627884531946</v>
+        <v>0.7314899502036275</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.192118114448986</v>
+        <v>8.170771657287988</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08510430354284315</v>
+        <v>0.08507837300169949</v>
       </c>
       <c r="C11">
-        <v>78.05655688944178</v>
+        <v>77.28757244943262</v>
       </c>
       <c r="D11">
-        <v>82.20555688944178</v>
+        <v>82.25757244943262</v>
       </c>
       <c r="E11">
-        <v>-10.911</v>
+        <v>-10.09</v>
       </c>
       <c r="F11">
-        <v>7.388999999999999</v>
+        <v>8.209999999999999</v>
       </c>
       <c r="G11">
         <v>3.24</v>
@@ -2177,45 +2177,45 @@
         <v>3.23</v>
       </c>
       <c r="M11">
-        <v>0.3953115</v>
+        <v>0.4458029999999999</v>
       </c>
       <c r="N11">
-        <v>2.8346885</v>
+        <v>2.784197000000001</v>
       </c>
       <c r="O11">
-        <v>0.51024393</v>
+        <v>0.5011554600000001</v>
       </c>
       <c r="P11">
-        <v>2.32444457</v>
+        <v>2.283041540000001</v>
       </c>
       <c r="Q11">
-        <v>7.83444457</v>
+        <v>7.793041540000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08918242147565181</v>
+        <v>0.08958419222411054</v>
       </c>
       <c r="T11">
-        <v>0.7314899502036275</v>
+        <v>0.738264382215181</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.18</v>
       </c>
       <c r="W11">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.170771657287988</v>
+        <v>7.245352767926643</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08507837300169949</v>
+        <v>0.08499340246055585</v>
       </c>
       <c r="C12">
-        <v>77.28757244943262</v>
+        <v>76.63748195127422</v>
       </c>
       <c r="D12">
-        <v>82.25757244943262</v>
+        <v>82.42848195127424</v>
       </c>
       <c r="E12">
-        <v>-10.09</v>
+        <v>-9.269000000000002</v>
       </c>
       <c r="F12">
-        <v>8.209999999999999</v>
+        <v>9.030999999999999</v>
       </c>
       <c r="G12">
         <v>3.24</v>
@@ -2259,28 +2259,28 @@
         <v>3.23</v>
       </c>
       <c r="M12">
-        <v>0.4458029999999999</v>
+        <v>0.4903833</v>
       </c>
       <c r="N12">
-        <v>2.784197000000001</v>
+        <v>2.7396167</v>
       </c>
       <c r="O12">
-        <v>0.5011554600000001</v>
+        <v>0.493131006</v>
       </c>
       <c r="P12">
-        <v>2.283041540000001</v>
+        <v>2.246485694</v>
       </c>
       <c r="Q12">
-        <v>7.793041540000001</v>
+        <v>7.756485694</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08958419222411054</v>
+        <v>0.08999499152871443</v>
       </c>
       <c r="T12">
-        <v>0.738264382215181</v>
+        <v>0.7451910486539605</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.245352767926643</v>
+        <v>6.586684334478766</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08499340246055585</v>
+        <v>0.0850068319194122</v>
       </c>
       <c r="C13">
-        <v>76.63748195127422</v>
+        <v>75.78942273842573</v>
       </c>
       <c r="D13">
-        <v>82.42848195127424</v>
+        <v>82.40142273842574</v>
       </c>
       <c r="E13">
-        <v>-9.269000000000002</v>
+        <v>-8.448000000000002</v>
       </c>
       <c r="F13">
-        <v>9.030999999999999</v>
+        <v>9.851999999999999</v>
       </c>
       <c r="G13">
         <v>3.24</v>
@@ -2341,45 +2341,45 @@
         <v>3.23</v>
       </c>
       <c r="M13">
-        <v>0.4903833</v>
+        <v>0.5448156</v>
       </c>
       <c r="N13">
-        <v>2.7396167</v>
+        <v>2.685184400000001</v>
       </c>
       <c r="O13">
-        <v>0.493131006</v>
+        <v>0.4833331920000001</v>
       </c>
       <c r="P13">
-        <v>2.246485694</v>
+        <v>2.201851208000001</v>
       </c>
       <c r="Q13">
-        <v>7.756485694</v>
+        <v>7.711851208000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08999499152871443</v>
+        <v>0.09041512718115023</v>
       </c>
       <c r="T13">
-        <v>0.7451910486539605</v>
+        <v>0.7522751393299849</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.18</v>
       </c>
       <c r="W13">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.586684334478766</v>
+        <v>5.928611442109956</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0850068319194122</v>
+        <v>0.08493006137826856</v>
       </c>
       <c r="C14">
-        <v>75.78942273842573</v>
+        <v>75.12334877948604</v>
       </c>
       <c r="D14">
-        <v>82.40142273842574</v>
+        <v>82.55634877948604</v>
       </c>
       <c r="E14">
-        <v>-8.448000000000002</v>
+        <v>-7.627000000000001</v>
       </c>
       <c r="F14">
-        <v>9.851999999999999</v>
+        <v>10.673</v>
       </c>
       <c r="G14">
         <v>3.24</v>
@@ -2423,28 +2423,28 @@
         <v>3.23</v>
       </c>
       <c r="M14">
-        <v>0.5448156</v>
+        <v>0.5902169</v>
       </c>
       <c r="N14">
-        <v>2.685184400000001</v>
+        <v>2.6397831</v>
       </c>
       <c r="O14">
-        <v>0.4833331920000001</v>
+        <v>0.475160958</v>
       </c>
       <c r="P14">
-        <v>2.201851208000001</v>
+        <v>2.164622142</v>
       </c>
       <c r="Q14">
-        <v>7.711851208000001</v>
+        <v>7.674622142</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09041512718115023</v>
+        <v>0.09084492112444661</v>
       </c>
       <c r="T14">
-        <v>0.7522751393299849</v>
+        <v>0.7595220826652284</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.928611442109956</v>
+        <v>5.472564408101497</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08493006137826856</v>
+        <v>0.08485329083712492</v>
       </c>
       <c r="C15">
-        <v>75.12334877948604</v>
+        <v>74.45785848256628</v>
       </c>
       <c r="D15">
-        <v>82.55634877948604</v>
+        <v>82.71185848256629</v>
       </c>
       <c r="E15">
-        <v>-7.627000000000001</v>
+        <v>-6.806000000000001</v>
       </c>
       <c r="F15">
-        <v>10.673</v>
+        <v>11.494</v>
       </c>
       <c r="G15">
         <v>3.24</v>
@@ -2505,28 +2505,28 @@
         <v>3.23</v>
       </c>
       <c r="M15">
-        <v>0.5902169</v>
+        <v>0.6356182</v>
       </c>
       <c r="N15">
-        <v>2.6397831</v>
+        <v>2.5943818</v>
       </c>
       <c r="O15">
-        <v>0.475160958</v>
+        <v>0.466988724</v>
       </c>
       <c r="P15">
-        <v>2.164622142</v>
+        <v>2.127393076</v>
       </c>
       <c r="Q15">
-        <v>7.674622142</v>
+        <v>7.637393076</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09084492112444661</v>
+        <v>0.09128471027572665</v>
       </c>
       <c r="T15">
-        <v>0.7595220826652284</v>
+        <v>0.7669375595664076</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.472564408101497</v>
+        <v>5.081666950379961</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08485329083712492</v>
+        <v>0.08477652029598126</v>
       </c>
       <c r="C16">
-        <v>74.45785848256628</v>
+        <v>73.79295515218779</v>
       </c>
       <c r="D16">
-        <v>82.71185848256629</v>
+        <v>82.86795515218779</v>
       </c>
       <c r="E16">
-        <v>-6.806000000000001</v>
+        <v>-5.984999999999999</v>
       </c>
       <c r="F16">
-        <v>11.494</v>
+        <v>12.315</v>
       </c>
       <c r="G16">
         <v>3.24</v>
@@ -2587,28 +2587,28 @@
         <v>3.23</v>
       </c>
       <c r="M16">
-        <v>0.6356182</v>
+        <v>0.6810195000000001</v>
       </c>
       <c r="N16">
-        <v>2.5943818</v>
+        <v>2.5489805</v>
       </c>
       <c r="O16">
-        <v>0.466988724</v>
+        <v>0.45881649</v>
       </c>
       <c r="P16">
-        <v>2.127393076</v>
+        <v>2.090164010000001</v>
       </c>
       <c r="Q16">
-        <v>7.637393076</v>
+        <v>7.60016401</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09128471027572665</v>
+        <v>0.09173484740703679</v>
       </c>
       <c r="T16">
-        <v>0.7669375595664076</v>
+        <v>0.7745275182770265</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.081666950379961</v>
+        <v>4.742889153687964</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08477652029598126</v>
+        <v>0.08502774975483762</v>
       </c>
       <c r="C17">
-        <v>73.79295515218779</v>
+        <v>72.46331045526472</v>
       </c>
       <c r="D17">
-        <v>82.86795515218779</v>
+        <v>82.35931045526472</v>
       </c>
       <c r="E17">
-        <v>-5.985000000000001</v>
+        <v>-5.164000000000001</v>
       </c>
       <c r="F17">
-        <v>12.315</v>
+        <v>13.136</v>
       </c>
       <c r="G17">
         <v>3.24</v>
@@ -2669,45 +2669,45 @@
         <v>3.23</v>
       </c>
       <c r="M17">
-        <v>0.6810195</v>
+        <v>0.7592608</v>
       </c>
       <c r="N17">
-        <v>2.5489805</v>
+        <v>2.470739200000001</v>
       </c>
       <c r="O17">
-        <v>0.45881649</v>
+        <v>0.4447330560000001</v>
       </c>
       <c r="P17">
-        <v>2.090164010000001</v>
+        <v>2.026006144000001</v>
       </c>
       <c r="Q17">
-        <v>7.60016401</v>
+        <v>7.536006144</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09173484740703679</v>
+        <v>0.09219570208909242</v>
       </c>
       <c r="T17">
-        <v>0.7745275182770265</v>
+        <v>0.782298190290279</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.18</v>
       </c>
       <c r="W17">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.742889153687964</v>
+        <v>4.254137708676651</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08502774975483762</v>
+        <v>0.08497147921369398</v>
       </c>
       <c r="C18">
-        <v>72.46331045526472</v>
+        <v>71.75569362831851</v>
       </c>
       <c r="D18">
-        <v>82.35931045526472</v>
+        <v>82.47269362831852</v>
       </c>
       <c r="E18">
-        <v>-5.164000000000001</v>
+        <v>-4.343</v>
       </c>
       <c r="F18">
-        <v>13.136</v>
+        <v>13.957</v>
       </c>
       <c r="G18">
         <v>3.24</v>
@@ -2751,28 +2751,28 @@
         <v>3.23</v>
       </c>
       <c r="M18">
-        <v>0.7592608</v>
+        <v>0.8067146000000001</v>
       </c>
       <c r="N18">
-        <v>2.470739200000001</v>
+        <v>2.4232854</v>
       </c>
       <c r="O18">
-        <v>0.4447330560000001</v>
+        <v>0.436191372</v>
       </c>
       <c r="P18">
-        <v>2.026006144000001</v>
+        <v>1.987094028</v>
       </c>
       <c r="Q18">
-        <v>7.536006144</v>
+        <v>7.497094027999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09219570208909242</v>
+        <v>0.09266766170324575</v>
       </c>
       <c r="T18">
-        <v>0.782298190290279</v>
+        <v>0.7902561074122847</v>
       </c>
       <c r="U18">
         <v>0.0578</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.254137708676651</v>
+        <v>4.003894314048612</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08497147921369398</v>
+        <v>0.08543180867255035</v>
       </c>
       <c r="C19">
-        <v>71.75569362831851</v>
+        <v>70.01621303828018</v>
       </c>
       <c r="D19">
-        <v>82.47269362831852</v>
+        <v>81.5542130382802</v>
       </c>
       <c r="E19">
-        <v>-4.343</v>
+        <v>-3.522</v>
       </c>
       <c r="F19">
-        <v>13.957</v>
+        <v>14.778</v>
       </c>
       <c r="G19">
         <v>3.24</v>
@@ -2833,45 +2833,45 @@
         <v>3.23</v>
       </c>
       <c r="M19">
-        <v>0.8067146000000001</v>
+        <v>0.9058914</v>
       </c>
       <c r="N19">
-        <v>2.4232854</v>
+        <v>2.324108600000001</v>
       </c>
       <c r="O19">
-        <v>0.436191372</v>
+        <v>0.4183395480000001</v>
       </c>
       <c r="P19">
-        <v>1.987094028</v>
+        <v>1.905769052000001</v>
       </c>
       <c r="Q19">
-        <v>7.497094027999999</v>
+        <v>7.415769052</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09266766170324575</v>
+        <v>0.09315113252750042</v>
       </c>
       <c r="T19">
-        <v>0.7902561074122847</v>
+        <v>0.7984081200738516</v>
       </c>
       <c r="U19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V19">
         <v>0.18</v>
       </c>
       <c r="W19">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.003894314048612</v>
+        <v>3.565548806402181</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08543180867255035</v>
+        <v>0.0858404781314067</v>
       </c>
       <c r="C20">
-        <v>70.0162130382802</v>
+        <v>68.39678303128524</v>
       </c>
       <c r="D20">
-        <v>81.5542130382802</v>
+        <v>80.75578303128525</v>
       </c>
       <c r="E20">
-        <v>-3.522000000000002</v>
+        <v>-2.701000000000002</v>
       </c>
       <c r="F20">
-        <v>14.778</v>
+        <v>15.599</v>
       </c>
       <c r="G20">
         <v>3.24</v>
@@ -2915,45 +2915,45 @@
         <v>3.23</v>
       </c>
       <c r="M20">
-        <v>0.9058913999999999</v>
+        <v>0.9998958999999999</v>
       </c>
       <c r="N20">
-        <v>2.324108600000001</v>
+        <v>2.230104100000001</v>
       </c>
       <c r="O20">
-        <v>0.4183395480000001</v>
+        <v>0.4014187380000001</v>
       </c>
       <c r="P20">
-        <v>1.905769052000001</v>
+        <v>1.828685362000001</v>
       </c>
       <c r="Q20">
-        <v>7.415769052</v>
+        <v>7.338685362000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0931511325275004</v>
+        <v>0.09364654090297123</v>
       </c>
       <c r="T20">
-        <v>0.7984081200738514</v>
+        <v>0.8067614169986669</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0.18</v>
       </c>
       <c r="W20">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.565548806402181</v>
+        <v>3.230336278006541</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0858404781314067</v>
+        <v>0.08583586759026306</v>
       </c>
       <c r="C21">
-        <v>68.39678303128524</v>
+        <v>67.5847035841615</v>
       </c>
       <c r="D21">
-        <v>80.75578303128525</v>
+        <v>80.76470358416151</v>
       </c>
       <c r="E21">
-        <v>-2.701000000000002</v>
+        <v>-1.880000000000003</v>
       </c>
       <c r="F21">
-        <v>15.599</v>
+        <v>16.42</v>
       </c>
       <c r="G21">
         <v>3.24</v>
@@ -2997,28 +2997,28 @@
         <v>3.23</v>
       </c>
       <c r="M21">
-        <v>0.9998958999999999</v>
+        <v>1.052522</v>
       </c>
       <c r="N21">
-        <v>2.230104100000001</v>
+        <v>2.177478000000001</v>
       </c>
       <c r="O21">
-        <v>0.4014187380000001</v>
+        <v>0.3919460400000001</v>
       </c>
       <c r="P21">
-        <v>1.828685362000001</v>
+        <v>1.785531960000001</v>
       </c>
       <c r="Q21">
-        <v>7.338685362000001</v>
+        <v>7.29553196</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09364654090297123</v>
+        <v>0.09415433448782881</v>
       </c>
       <c r="T21">
-        <v>0.8067614169986669</v>
+        <v>0.8153235463466026</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.230336278006541</v>
+        <v>3.068819464106214</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08583586759026306</v>
+        <v>0.08717441704911941</v>
       </c>
       <c r="C22">
-        <v>67.5847035841615</v>
+        <v>64.25405417171233</v>
       </c>
       <c r="D22">
-        <v>80.76470358416151</v>
+        <v>78.25505417171233</v>
       </c>
       <c r="E22">
-        <v>-1.880000000000003</v>
+        <v>-1.059000000000001</v>
       </c>
       <c r="F22">
-        <v>16.42</v>
+        <v>17.241</v>
       </c>
       <c r="G22">
         <v>3.24</v>
@@ -3079,45 +3079,45 @@
         <v>3.23</v>
       </c>
       <c r="M22">
-        <v>1.052522</v>
+        <v>1.2396279</v>
       </c>
       <c r="N22">
-        <v>2.177478000000001</v>
+        <v>1.9903721</v>
       </c>
       <c r="O22">
-        <v>0.3919460400000001</v>
+        <v>0.3582669780000001</v>
       </c>
       <c r="P22">
-        <v>1.785531960000001</v>
+        <v>1.632105122</v>
       </c>
       <c r="Q22">
-        <v>7.29553196</v>
+        <v>7.142105122</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09415433448782881</v>
+        <v>0.09467498360648025</v>
       </c>
       <c r="T22">
-        <v>0.8153235463466026</v>
+        <v>0.8241024384628405</v>
       </c>
       <c r="U22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V22">
         <v>0.18</v>
       </c>
       <c r="W22">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.068819464106214</v>
+        <v>2.605620605989911</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08717441704911941</v>
+        <v>0.08793732650797577</v>
       </c>
       <c r="C23">
-        <v>64.25405417171233</v>
+        <v>62.07123894848952</v>
       </c>
       <c r="D23">
-        <v>78.25505417171233</v>
+        <v>76.89323894848953</v>
       </c>
       <c r="E23">
-        <v>-1.059000000000001</v>
+        <v>-0.2380000000000031</v>
       </c>
       <c r="F23">
-        <v>17.241</v>
+        <v>18.062</v>
       </c>
       <c r="G23">
         <v>3.24</v>
@@ -3161,45 +3161,45 @@
         <v>3.23</v>
       </c>
       <c r="M23">
-        <v>1.2396279</v>
+        <v>1.3690996</v>
       </c>
       <c r="N23">
-        <v>1.9903721</v>
+        <v>1.8609004</v>
       </c>
       <c r="O23">
-        <v>0.3582669780000001</v>
+        <v>0.3349620720000001</v>
       </c>
       <c r="P23">
-        <v>1.632105122</v>
+        <v>1.525938328000001</v>
       </c>
       <c r="Q23">
-        <v>7.142105122</v>
+        <v>7.035938328</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09467498360648025</v>
+        <v>0.09520898270253303</v>
       </c>
       <c r="T23">
-        <v>0.8241024384628405</v>
+        <v>0.8331064303769307</v>
       </c>
       <c r="U23">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V23">
         <v>0.18</v>
       </c>
       <c r="W23">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.605620605989911</v>
+        <v>2.35921477151845</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08793732650797577</v>
+        <v>0.08802865596683211</v>
       </c>
       <c r="C24">
-        <v>62.07123894848952</v>
+        <v>61.09038328755094</v>
       </c>
       <c r="D24">
-        <v>76.89323894848953</v>
+        <v>76.73338328755094</v>
       </c>
       <c r="E24">
-        <v>-0.2380000000000031</v>
+        <v>0.5829999999999984</v>
       </c>
       <c r="F24">
-        <v>18.062</v>
+        <v>18.883</v>
       </c>
       <c r="G24">
         <v>3.24</v>
@@ -3243,28 +3243,28 @@
         <v>3.23</v>
       </c>
       <c r="M24">
-        <v>1.3690996</v>
+        <v>1.4313314</v>
       </c>
       <c r="N24">
-        <v>1.8609004</v>
+        <v>1.7986686</v>
       </c>
       <c r="O24">
-        <v>0.3349620720000001</v>
+        <v>0.323760348</v>
       </c>
       <c r="P24">
-        <v>1.525938328000001</v>
+        <v>1.474908252</v>
       </c>
       <c r="Q24">
-        <v>7.035938328</v>
+        <v>6.984908252</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09520898270253303</v>
+        <v>0.09575685190497676</v>
       </c>
       <c r="T24">
-        <v>0.8331064303769307</v>
+        <v>0.8423442922108674</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.35921477151845</v>
+        <v>2.256640216235038</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08802865596683211</v>
+        <v>0.08811998542568848</v>
       </c>
       <c r="C25">
-        <v>61.09038328755094</v>
+        <v>60.11019090515975</v>
       </c>
       <c r="D25">
-        <v>76.73338328755094</v>
+        <v>76.57419090515975</v>
       </c>
       <c r="E25">
-        <v>0.5829999999999984</v>
+        <v>1.404</v>
       </c>
       <c r="F25">
-        <v>18.883</v>
+        <v>19.704</v>
       </c>
       <c r="G25">
         <v>3.24</v>
@@ -3325,28 +3325,28 @@
         <v>3.23</v>
       </c>
       <c r="M25">
-        <v>1.4313314</v>
+        <v>1.4935632</v>
       </c>
       <c r="N25">
-        <v>1.7986686</v>
+        <v>1.7364368</v>
       </c>
       <c r="O25">
-        <v>0.323760348</v>
+        <v>0.3125586240000001</v>
       </c>
       <c r="P25">
-        <v>1.474908252</v>
+        <v>1.423878176</v>
       </c>
       <c r="Q25">
-        <v>6.984908252</v>
+        <v>6.933878176</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09575685190497676</v>
+        <v>0.09631913871801115</v>
       </c>
       <c r="T25">
-        <v>0.8423442922108674</v>
+        <v>0.8518252556720129</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.256640216235038</v>
+        <v>2.162613540558579</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08811998542568848</v>
+        <v>0.08821131488454481</v>
       </c>
       <c r="C26">
-        <v>60.11019090515975</v>
+        <v>59.1306576817158</v>
       </c>
       <c r="D26">
-        <v>76.57419090515975</v>
+        <v>76.4156576817158</v>
       </c>
       <c r="E26">
-        <v>1.403999999999996</v>
+        <v>2.224999999999998</v>
       </c>
       <c r="F26">
-        <v>19.704</v>
+        <v>20.525</v>
       </c>
       <c r="G26">
         <v>3.24</v>
@@ -3407,28 +3407,28 @@
         <v>3.23</v>
       </c>
       <c r="M26">
-        <v>1.4935632</v>
+        <v>1.555795</v>
       </c>
       <c r="N26">
-        <v>1.736436800000001</v>
+        <v>1.674205</v>
       </c>
       <c r="O26">
-        <v>0.3125586240000001</v>
+        <v>0.3013569</v>
       </c>
       <c r="P26">
-        <v>1.423878176000001</v>
+        <v>1.3728481</v>
       </c>
       <c r="Q26">
-        <v>6.933878176</v>
+        <v>6.8828481</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09631913871801115</v>
+        <v>0.09689641984605976</v>
       </c>
       <c r="T26">
-        <v>0.8518252556720128</v>
+        <v>0.8615590448254556</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.162613540558579</v>
+        <v>2.076108998936236</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08821131488454481</v>
+        <v>0.09133008434340117</v>
       </c>
       <c r="C27">
-        <v>59.1306576817158</v>
+        <v>53.26391128539373</v>
       </c>
       <c r="D27">
-        <v>76.4156576817158</v>
+        <v>71.36991128539374</v>
       </c>
       <c r="E27">
-        <v>2.224999999999998</v>
+        <v>3.045999999999999</v>
       </c>
       <c r="F27">
-        <v>20.525</v>
+        <v>21.346</v>
       </c>
       <c r="G27">
         <v>3.24</v>
@@ -3489,45 +3489,45 @@
         <v>3.23</v>
       </c>
       <c r="M27">
-        <v>1.555795</v>
+        <v>1.92114</v>
       </c>
       <c r="N27">
-        <v>1.674205</v>
+        <v>1.308860000000001</v>
       </c>
       <c r="O27">
-        <v>0.3013569</v>
+        <v>0.2355948000000001</v>
       </c>
       <c r="P27">
-        <v>1.3728481</v>
+        <v>1.0732652</v>
       </c>
       <c r="Q27">
-        <v>6.8828481</v>
+        <v>6.5832652</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09689641984605976</v>
+        <v>0.09748930316675836</v>
       </c>
       <c r="T27">
-        <v>0.8615590448254556</v>
+        <v>0.8715559093614238</v>
       </c>
       <c r="U27">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V27">
         <v>0.18</v>
       </c>
       <c r="W27">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.076108998936236</v>
+        <v>1.681293398711182</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09133008434340117</v>
+        <v>0.09153785380225753</v>
       </c>
       <c r="C28">
-        <v>53.26391128539373</v>
+        <v>52.13033902077861</v>
       </c>
       <c r="D28">
-        <v>71.36991128539374</v>
+        <v>71.05733902077861</v>
       </c>
       <c r="E28">
-        <v>3.045999999999999</v>
+        <v>3.867000000000001</v>
       </c>
       <c r="F28">
-        <v>21.346</v>
+        <v>22.167</v>
       </c>
       <c r="G28">
         <v>3.24</v>
@@ -3571,28 +3571,28 @@
         <v>3.23</v>
       </c>
       <c r="M28">
-        <v>1.92114</v>
+        <v>1.99503</v>
       </c>
       <c r="N28">
-        <v>1.308860000000001</v>
+        <v>1.23497</v>
       </c>
       <c r="O28">
-        <v>0.2355948000000001</v>
+        <v>0.2222946000000001</v>
       </c>
       <c r="P28">
-        <v>1.0732652</v>
+        <v>1.0126754</v>
       </c>
       <c r="Q28">
-        <v>6.5832652</v>
+        <v>6.5226754</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09748930316675836</v>
+        <v>0.0980984298661062</v>
       </c>
       <c r="T28">
-        <v>0.8715559093614238</v>
+        <v>0.8818266605970075</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.681293398711182</v>
+        <v>1.61902327283299</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09153785380225753</v>
+        <v>0.09174562326111389</v>
       </c>
       <c r="C29">
-        <v>52.13033902077861</v>
+        <v>50.99949270581719</v>
       </c>
       <c r="D29">
-        <v>71.05733902077861</v>
+        <v>70.74749270581719</v>
       </c>
       <c r="E29">
-        <v>3.867000000000001</v>
+        <v>4.687999999999999</v>
       </c>
       <c r="F29">
-        <v>22.167</v>
+        <v>22.988</v>
       </c>
       <c r="G29">
         <v>3.24</v>
@@ -3653,28 +3653,28 @@
         <v>3.23</v>
       </c>
       <c r="M29">
-        <v>1.99503</v>
+        <v>2.06892</v>
       </c>
       <c r="N29">
-        <v>1.23497</v>
+        <v>1.161080000000001</v>
       </c>
       <c r="O29">
-        <v>0.2222946000000001</v>
+        <v>0.2089944000000001</v>
       </c>
       <c r="P29">
-        <v>1.0126754</v>
+        <v>0.9520856000000004</v>
       </c>
       <c r="Q29">
-        <v>6.5226754</v>
+        <v>6.4620856</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0980984298661062</v>
+        <v>0.09872447675154708</v>
       </c>
       <c r="T29">
-        <v>0.8818266605970075</v>
+        <v>0.8923827104780243</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.61902327283299</v>
+        <v>1.561201013088955</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09174562326111389</v>
+        <v>0.09195339271997024</v>
       </c>
       <c r="C30">
-        <v>50.99949270581719</v>
+        <v>49.87133683572746</v>
       </c>
       <c r="D30">
-        <v>70.74749270581719</v>
+        <v>70.44033683572746</v>
       </c>
       <c r="E30">
-        <v>4.687999999999999</v>
+        <v>5.509</v>
       </c>
       <c r="F30">
-        <v>22.988</v>
+        <v>23.809</v>
       </c>
       <c r="G30">
         <v>3.24</v>
@@ -3735,28 +3735,28 @@
         <v>3.23</v>
       </c>
       <c r="M30">
-        <v>2.06892</v>
+        <v>2.14281</v>
       </c>
       <c r="N30">
-        <v>1.161080000000001</v>
+        <v>1.087190000000001</v>
       </c>
       <c r="O30">
-        <v>0.2089944000000001</v>
+        <v>0.1956942000000001</v>
       </c>
       <c r="P30">
-        <v>0.9520856000000004</v>
+        <v>0.8914958000000004</v>
       </c>
       <c r="Q30">
-        <v>6.4620856</v>
+        <v>6.4014958</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09872447675154708</v>
+        <v>0.09936815876052146</v>
       </c>
       <c r="T30">
-        <v>0.8923827104780243</v>
+        <v>0.903236113876816</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.561201013088955</v>
+        <v>1.507366495396232</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09195339271997024</v>
+        <v>0.1072106987314992</v>
       </c>
       <c r="C31">
-        <v>49.87133683572746</v>
+        <v>32.02168714961971</v>
       </c>
       <c r="D31">
-        <v>70.44033683572746</v>
+        <v>53.41168714961971</v>
       </c>
       <c r="E31">
-        <v>5.508999999999997</v>
+        <v>6.329999999999998</v>
       </c>
       <c r="F31">
-        <v>23.809</v>
+        <v>24.63</v>
       </c>
       <c r="G31">
         <v>3.24</v>
@@ -3817,45 +3817,45 @@
         <v>3.23</v>
       </c>
       <c r="M31">
-        <v>2.14281</v>
+        <v>3.615684</v>
       </c>
       <c r="N31">
-        <v>1.087190000000001</v>
+        <v>-0.3856839999999999</v>
       </c>
       <c r="O31">
-        <v>0.1956942000000001</v>
+        <v>-0.06942311999999998</v>
       </c>
       <c r="P31">
-        <v>0.8914958000000004</v>
+        <v>-0.31626088</v>
       </c>
       <c r="Q31">
-        <v>6.4014958</v>
+        <v>5.19373912</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09936815876052146</v>
+        <v>0.1003604378955295</v>
       </c>
       <c r="T31">
-        <v>0.903236113876816</v>
+        <v>0.9199673656226992</v>
       </c>
       <c r="U31">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.18</v>
+        <v>0.1607994503944482</v>
       </c>
       <c r="W31">
-        <v>0.0738</v>
+        <v>0.123194640682095</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.507366495396232</v>
+        <v>0.8933302799691566</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1072106987314992</v>
+        <v>0.1082206987314992</v>
       </c>
       <c r="C32">
-        <v>32.02168714961971</v>
+        <v>30.35940127665861</v>
       </c>
       <c r="D32">
-        <v>53.41168714961971</v>
+        <v>52.57040127665861</v>
       </c>
       <c r="E32">
-        <v>6.329999999999998</v>
+        <v>7.150999999999996</v>
       </c>
       <c r="F32">
-        <v>24.63</v>
+        <v>25.451</v>
       </c>
       <c r="G32">
         <v>3.24</v>
@@ -3899,37 +3899,37 @@
         <v>3.23</v>
       </c>
       <c r="M32">
-        <v>3.615684</v>
+        <v>3.7362068</v>
       </c>
       <c r="N32">
-        <v>-0.3856839999999999</v>
+        <v>-0.5062067999999993</v>
       </c>
       <c r="O32">
-        <v>-0.06942311999999998</v>
+        <v>-0.09111722399999987</v>
       </c>
       <c r="P32">
-        <v>-0.31626088</v>
+        <v>-0.4150895759999994</v>
       </c>
       <c r="Q32">
-        <v>5.19373912</v>
+        <v>5.094910424</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1003604378955295</v>
+        <v>0.1011511688795227</v>
       </c>
       <c r="T32">
-        <v>0.9199673656226992</v>
+        <v>0.9333002259940426</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.1607994503944482</v>
+        <v>0.155612371349466</v>
       </c>
       <c r="W32">
-        <v>0.123194640682095</v>
+        <v>0.1239561038858984</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8933302799691566</v>
+        <v>0.8645131741637001</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1082206987314992</v>
+        <v>0.1092306987314992</v>
       </c>
       <c r="C33">
-        <v>30.35940127665861</v>
+        <v>28.72320657918942</v>
       </c>
       <c r="D33">
-        <v>52.57040127665861</v>
+        <v>51.75520657918941</v>
       </c>
       <c r="E33">
-        <v>7.150999999999996</v>
+        <v>7.971999999999998</v>
       </c>
       <c r="F33">
-        <v>25.451</v>
+        <v>26.272</v>
       </c>
       <c r="G33">
         <v>3.24</v>
@@ -3981,37 +3981,37 @@
         <v>3.23</v>
       </c>
       <c r="M33">
-        <v>3.7362068</v>
+        <v>3.8567296</v>
       </c>
       <c r="N33">
-        <v>-0.5062067999999993</v>
+        <v>-0.6267295999999996</v>
       </c>
       <c r="O33">
-        <v>-0.09111722399999987</v>
+        <v>-0.1128113279999999</v>
       </c>
       <c r="P33">
-        <v>-0.4150895759999994</v>
+        <v>-0.5139182719999996</v>
       </c>
       <c r="Q33">
-        <v>5.094910424</v>
+        <v>4.996081728</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1011511688795227</v>
+        <v>0.1019651566571627</v>
       </c>
       <c r="T33">
-        <v>0.9333002259940426</v>
+        <v>0.9470252293174846</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.155612371349466</v>
+        <v>0.1507494847447952</v>
       </c>
       <c r="W33">
-        <v>0.1239561038858984</v>
+        <v>0.1246699756394641</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8645131741637001</v>
+        <v>0.8374971374710845</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1092306987314992</v>
+        <v>0.1102406987314992</v>
       </c>
       <c r="C34">
-        <v>28.72320657918942</v>
+        <v>27.111907825379</v>
       </c>
       <c r="D34">
-        <v>51.75520657918941</v>
+        <v>50.96490782537899</v>
       </c>
       <c r="E34">
-        <v>7.971999999999998</v>
+        <v>8.792999999999999</v>
       </c>
       <c r="F34">
-        <v>26.272</v>
+        <v>27.093</v>
       </c>
       <c r="G34">
         <v>3.24</v>
@@ -4063,37 +4063,37 @@
         <v>3.23</v>
       </c>
       <c r="M34">
-        <v>3.8567296</v>
+        <v>3.9772524</v>
       </c>
       <c r="N34">
-        <v>-0.6267295999999996</v>
+        <v>-0.7472523999999998</v>
       </c>
       <c r="O34">
-        <v>-0.1128113279999999</v>
+        <v>-0.134505432</v>
       </c>
       <c r="P34">
-        <v>-0.5139182719999996</v>
+        <v>-0.6127469679999998</v>
       </c>
       <c r="Q34">
-        <v>4.996081728</v>
+        <v>4.897253032</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1019651566571627</v>
+        <v>0.1028034425774189</v>
       </c>
       <c r="T34">
-        <v>0.9470252293174846</v>
+        <v>0.9611599342326708</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.1507494847447952</v>
+        <v>0.1461813185404074</v>
       </c>
       <c r="W34">
-        <v>0.1246699756394641</v>
+        <v>0.1253405824382682</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8374971374710845</v>
+        <v>0.812118436335597</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1102406987314992</v>
+        <v>0.1301312748363713</v>
       </c>
       <c r="C35">
-        <v>27.111907825379</v>
+        <v>14.50805508750552</v>
       </c>
       <c r="D35">
-        <v>50.96490782537899</v>
+        <v>39.18205508750552</v>
       </c>
       <c r="E35">
-        <v>8.792999999999999</v>
+        <v>9.614000000000001</v>
       </c>
       <c r="F35">
-        <v>27.093</v>
+        <v>27.914</v>
       </c>
       <c r="G35">
         <v>3.24</v>
@@ -4145,45 +4145,45 @@
         <v>3.23</v>
       </c>
       <c r="M35">
-        <v>3.9772524</v>
+        <v>5.605131200000001</v>
       </c>
       <c r="N35">
-        <v>-0.7472523999999998</v>
+        <v>-2.3751312</v>
       </c>
       <c r="O35">
-        <v>-0.134505432</v>
+        <v>-0.4275236160000001</v>
       </c>
       <c r="P35">
-        <v>-0.6127469679999998</v>
+        <v>-1.947607584</v>
       </c>
       <c r="Q35">
-        <v>4.897253032</v>
+        <v>3.562392416</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1028034425774189</v>
+        <v>0.1044558827753679</v>
       </c>
       <c r="T35">
-        <v>0.9611599342326708</v>
+        <v>0.9890224499013864</v>
       </c>
       <c r="U35">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1461813185404074</v>
+        <v>0.1037263855661398</v>
       </c>
       <c r="W35">
-        <v>0.1253405824382682</v>
+        <v>0.1799717417783191</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.812118436335597</v>
+        <v>0.5762576975896657</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1301312748363713</v>
+        <v>0.1316812748363713</v>
       </c>
       <c r="C36">
-        <v>14.50805508750552</v>
+        <v>12.9936355747574</v>
       </c>
       <c r="D36">
-        <v>39.18205508750552</v>
+        <v>38.4886355747574</v>
       </c>
       <c r="E36">
-        <v>9.614000000000001</v>
+        <v>10.435</v>
       </c>
       <c r="F36">
-        <v>27.914</v>
+        <v>28.735</v>
       </c>
       <c r="G36">
         <v>3.24</v>
@@ -4227,37 +4227,37 @@
         <v>3.23</v>
       </c>
       <c r="M36">
-        <v>5.605131200000001</v>
+        <v>5.769988</v>
       </c>
       <c r="N36">
-        <v>-2.3751312</v>
+        <v>-2.539987999999999</v>
       </c>
       <c r="O36">
-        <v>-0.4275236160000001</v>
+        <v>-0.4571978399999999</v>
       </c>
       <c r="P36">
-        <v>-1.947607584</v>
+        <v>-2.082790159999999</v>
       </c>
       <c r="Q36">
-        <v>3.562392416</v>
+        <v>3.427209840000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1044558827753679</v>
+        <v>0.105358280971912</v>
       </c>
       <c r="T36">
-        <v>0.9890224499013864</v>
+        <v>1.004238179899869</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1037263855661398</v>
+        <v>0.1007627745499644</v>
       </c>
       <c r="W36">
-        <v>0.1799717417783191</v>
+        <v>0.1805668348703671</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5762576975896657</v>
+        <v>0.5597931919442467</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1316812748363713</v>
+        <v>0.1332312748363713</v>
       </c>
       <c r="C37">
-        <v>12.9936355747574</v>
+        <v>11.50333267130258</v>
       </c>
       <c r="D37">
-        <v>38.4886355747574</v>
+        <v>37.81933267130258</v>
       </c>
       <c r="E37">
-        <v>10.435</v>
+        <v>11.256</v>
       </c>
       <c r="F37">
-        <v>28.735</v>
+        <v>29.556</v>
       </c>
       <c r="G37">
         <v>3.24</v>
@@ -4309,37 +4309,37 @@
         <v>3.23</v>
       </c>
       <c r="M37">
-        <v>5.769988</v>
+        <v>5.9348448</v>
       </c>
       <c r="N37">
-        <v>-2.539987999999999</v>
+        <v>-2.7048448</v>
       </c>
       <c r="O37">
-        <v>-0.4571978399999999</v>
+        <v>-0.486872064</v>
       </c>
       <c r="P37">
-        <v>-2.082790159999999</v>
+        <v>-2.217972736</v>
       </c>
       <c r="Q37">
-        <v>3.427209840000001</v>
+        <v>3.292027264</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.105358280971912</v>
+        <v>0.1062888791120981</v>
       </c>
       <c r="T37">
-        <v>1.004238179899869</v>
+        <v>1.019929401460805</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1007627745499644</v>
+        <v>0.09796380859024317</v>
       </c>
       <c r="W37">
-        <v>0.1805668348703671</v>
+        <v>0.1811288672350792</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5597931919442467</v>
+        <v>0.5442433810569065</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1332312748363713</v>
+        <v>0.1347812748363713</v>
       </c>
       <c r="C38">
-        <v>11.50333267130259</v>
+        <v>10.03590974539422</v>
       </c>
       <c r="D38">
-        <v>37.81933267130258</v>
+        <v>37.17290974539421</v>
       </c>
       <c r="E38">
-        <v>11.256</v>
+        <v>12.077</v>
       </c>
       <c r="F38">
-        <v>29.556</v>
+        <v>30.377</v>
       </c>
       <c r="G38">
         <v>3.24</v>
@@ -4391,37 +4391,37 @@
         <v>3.23</v>
       </c>
       <c r="M38">
-        <v>5.9348448</v>
+        <v>6.0997016</v>
       </c>
       <c r="N38">
-        <v>-2.704844799999999</v>
+        <v>-2.8697016</v>
       </c>
       <c r="O38">
-        <v>-0.4868720639999998</v>
+        <v>-0.516546288</v>
       </c>
       <c r="P38">
-        <v>-2.217972735999999</v>
+        <v>-2.353155312</v>
       </c>
       <c r="Q38">
-        <v>3.292027264000001</v>
+        <v>3.156844688</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1062888791120981</v>
+        <v>0.1072490200503854</v>
       </c>
       <c r="T38">
-        <v>1.019929401460805</v>
+        <v>1.036118757039548</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.09796380859024319</v>
+        <v>0.09531613808780416</v>
       </c>
       <c r="W38">
-        <v>0.1811288672350792</v>
+        <v>0.1816605194719689</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5442433810569066</v>
+        <v>0.5295341004878009</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1347812748363713</v>
+        <v>0.1363312748363713</v>
       </c>
       <c r="C39">
-        <v>10.03590974539422</v>
+        <v>8.59021329243053</v>
       </c>
       <c r="D39">
-        <v>37.17290974539421</v>
+        <v>36.54821329243052</v>
       </c>
       <c r="E39">
-        <v>12.077</v>
+        <v>12.898</v>
       </c>
       <c r="F39">
-        <v>30.377</v>
+        <v>31.198</v>
       </c>
       <c r="G39">
         <v>3.24</v>
@@ -4473,37 +4473,37 @@
         <v>3.23</v>
       </c>
       <c r="M39">
-        <v>6.0997016</v>
+        <v>6.264558399999999</v>
       </c>
       <c r="N39">
-        <v>-2.8697016</v>
+        <v>-3.034558399999999</v>
       </c>
       <c r="O39">
-        <v>-0.516546288</v>
+        <v>-0.5462205119999998</v>
       </c>
       <c r="P39">
-        <v>-2.353155312</v>
+        <v>-2.488337887999999</v>
       </c>
       <c r="Q39">
-        <v>3.156844688</v>
+        <v>3.021662112</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1072490200503854</v>
+        <v>0.1082401332770045</v>
       </c>
       <c r="T39">
-        <v>1.036118757039548</v>
+        <v>1.052830349895024</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.09531613808780416</v>
+        <v>0.09280781866444092</v>
       </c>
       <c r="W39">
-        <v>0.1816605194719689</v>
+        <v>0.1821641900121803</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5295341004878009</v>
+        <v>0.5155989925802273</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1363312748363713</v>
+        <v>0.1378812748363713</v>
       </c>
       <c r="C40">
-        <v>8.59021329243053</v>
+        <v>7.165166065573779</v>
       </c>
       <c r="D40">
-        <v>36.54821329243052</v>
+        <v>35.94416606557377</v>
       </c>
       <c r="E40">
-        <v>12.898</v>
+        <v>13.719</v>
       </c>
       <c r="F40">
-        <v>31.198</v>
+        <v>32.019</v>
       </c>
       <c r="G40">
         <v>3.24</v>
@@ -4555,37 +4555,37 @@
         <v>3.23</v>
       </c>
       <c r="M40">
-        <v>6.264558399999999</v>
+        <v>6.4294152</v>
       </c>
       <c r="N40">
-        <v>-3.034558399999999</v>
+        <v>-3.1994152</v>
       </c>
       <c r="O40">
-        <v>-0.5462205119999998</v>
+        <v>-0.575894736</v>
       </c>
       <c r="P40">
-        <v>-2.488337887999999</v>
+        <v>-2.623520464</v>
       </c>
       <c r="Q40">
-        <v>3.021662112</v>
+        <v>2.886479536</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1082401332770045</v>
+        <v>0.1092637420192505</v>
       </c>
       <c r="T40">
-        <v>1.052830349895024</v>
+        <v>1.070089863827729</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.09280781866444092</v>
+        <v>0.09042813100637831</v>
       </c>
       <c r="W40">
-        <v>0.1821641900121803</v>
+        <v>0.1826420312939192</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5155989925802273</v>
+        <v>0.5023785055909906</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1378812748363713</v>
+        <v>0.1536413335825492</v>
       </c>
       <c r="C41">
-        <v>7.165166065573779</v>
+        <v>1.172875326448633</v>
       </c>
       <c r="D41">
-        <v>35.94416606557377</v>
+        <v>30.77287532644863</v>
       </c>
       <c r="E41">
-        <v>13.719</v>
+        <v>14.54</v>
       </c>
       <c r="F41">
-        <v>32.019</v>
+        <v>32.84</v>
       </c>
       <c r="G41">
         <v>3.24</v>
@@ -4637,45 +4637,45 @@
         <v>3.23</v>
       </c>
       <c r="M41">
-        <v>6.4294152</v>
+        <v>7.743671999999999</v>
       </c>
       <c r="N41">
-        <v>-3.1994152</v>
+        <v>-4.513671999999999</v>
       </c>
       <c r="O41">
-        <v>-0.575894736</v>
+        <v>-0.8124609599999998</v>
       </c>
       <c r="P41">
-        <v>-2.623520464</v>
+        <v>-3.701211039999999</v>
       </c>
       <c r="Q41">
-        <v>2.886479536</v>
+        <v>1.808788960000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1092637420192505</v>
+        <v>0.1106715689632012</v>
       </c>
       <c r="T41">
-        <v>1.070089863827729</v>
+        <v>1.093827848617348</v>
       </c>
       <c r="U41">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.09042813100637831</v>
+        <v>0.07508065940809479</v>
       </c>
       <c r="W41">
-        <v>0.1826420312939192</v>
+        <v>0.2180959805115713</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.5023785055909906</v>
+        <v>0.4171147744894155</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1536413335825492</v>
+        <v>0.1555413335825492</v>
       </c>
       <c r="C42">
-        <v>1.172875326448633</v>
+        <v>-0.1727705584096668</v>
       </c>
       <c r="D42">
-        <v>30.77287532644863</v>
+        <v>30.24822944159034</v>
       </c>
       <c r="E42">
-        <v>14.54</v>
+        <v>15.361</v>
       </c>
       <c r="F42">
-        <v>32.84</v>
+        <v>33.661</v>
       </c>
       <c r="G42">
         <v>3.24</v>
@@ -4719,37 +4719,37 @@
         <v>3.23</v>
       </c>
       <c r="M42">
-        <v>7.743671999999999</v>
+        <v>7.9372638</v>
       </c>
       <c r="N42">
-        <v>-4.513671999999999</v>
+        <v>-4.7072638</v>
       </c>
       <c r="O42">
-        <v>-0.8124609599999998</v>
+        <v>-0.8473074839999999</v>
       </c>
       <c r="P42">
-        <v>-3.701211039999999</v>
+        <v>-3.859956316</v>
       </c>
       <c r="Q42">
-        <v>1.808788960000001</v>
+        <v>1.650043684</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1106715689632012</v>
+        <v>0.1117710870812216</v>
       </c>
       <c r="T42">
-        <v>1.093827848617348</v>
+        <v>1.112367303678659</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.07508065940809479</v>
+        <v>0.07324942381277538</v>
       </c>
       <c r="W42">
-        <v>0.2180959805115713</v>
+        <v>0.2185277858649476</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4171147744894155</v>
+        <v>0.4069412434043077</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1555413335825492</v>
+        <v>0.1574413335825492</v>
       </c>
       <c r="C43">
-        <v>-0.1727705584096668</v>
+        <v>-1.50082697970371</v>
       </c>
       <c r="D43">
-        <v>30.24822944159034</v>
+        <v>29.74117302029629</v>
       </c>
       <c r="E43">
-        <v>15.361</v>
+        <v>16.182</v>
       </c>
       <c r="F43">
-        <v>33.661</v>
+        <v>34.482</v>
       </c>
       <c r="G43">
         <v>3.24</v>
@@ -4801,37 +4801,37 @@
         <v>3.23</v>
       </c>
       <c r="M43">
-        <v>7.9372638</v>
+        <v>8.1308556</v>
       </c>
       <c r="N43">
-        <v>-4.7072638</v>
+        <v>-4.9008556</v>
       </c>
       <c r="O43">
-        <v>-0.8473074839999999</v>
+        <v>-0.882154008</v>
       </c>
       <c r="P43">
-        <v>-3.859956316</v>
+        <v>-4.018701592</v>
       </c>
       <c r="Q43">
-        <v>1.650043684</v>
+        <v>1.491298408</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1117710870812216</v>
+        <v>0.1129085196171047</v>
       </c>
       <c r="T43">
-        <v>1.112367303678659</v>
+        <v>1.131546050293809</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07324942381277538</v>
+        <v>0.07150538991247121</v>
       </c>
       <c r="W43">
-        <v>0.2185277858649476</v>
+        <v>0.2189390290586393</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4069412434043077</v>
+        <v>0.3972521661803956</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1574413335825492</v>
+        <v>0.1593413335825493</v>
       </c>
       <c r="C44">
-        <v>-1.50082697970371</v>
+        <v>-2.812163919636298</v>
       </c>
       <c r="D44">
-        <v>29.74117302029629</v>
+        <v>29.2508360803637</v>
       </c>
       <c r="E44">
-        <v>16.182</v>
+        <v>17.003</v>
       </c>
       <c r="F44">
-        <v>34.482</v>
+        <v>35.303</v>
       </c>
       <c r="G44">
         <v>3.24</v>
@@ -4883,37 +4883,37 @@
         <v>3.23</v>
       </c>
       <c r="M44">
-        <v>8.1308556</v>
+        <v>8.3244474</v>
       </c>
       <c r="N44">
-        <v>-4.9008556</v>
+        <v>-5.0944474</v>
       </c>
       <c r="O44">
-        <v>-0.882154008</v>
+        <v>-0.917000532</v>
       </c>
       <c r="P44">
-        <v>-4.018701592</v>
+        <v>-4.177446868</v>
       </c>
       <c r="Q44">
-        <v>1.491298408</v>
+        <v>1.332553132</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1129085196171047</v>
+        <v>0.1140858620665276</v>
       </c>
       <c r="T44">
-        <v>1.131546050293809</v>
+        <v>1.151397735386682</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.07150538991247121</v>
+        <v>0.06984247386799514</v>
       </c>
       <c r="W44">
-        <v>0.2189390290586393</v>
+        <v>0.2193311446619268</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3972521661803956</v>
+        <v>0.3880137437110841</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1593413335825493</v>
+        <v>0.1612413335825493</v>
       </c>
       <c r="C45">
-        <v>-2.812163919636298</v>
+        <v>-4.107594918054303</v>
       </c>
       <c r="D45">
-        <v>29.2508360803637</v>
+        <v>28.77640508194569</v>
       </c>
       <c r="E45">
-        <v>17.003</v>
+        <v>17.82399999999999</v>
       </c>
       <c r="F45">
-        <v>35.303</v>
+        <v>36.124</v>
       </c>
       <c r="G45">
         <v>3.24</v>
@@ -4965,37 +4965,37 @@
         <v>3.23</v>
       </c>
       <c r="M45">
-        <v>8.3244474</v>
+        <v>8.518039199999999</v>
       </c>
       <c r="N45">
-        <v>-5.0944474</v>
+        <v>-5.288039199999998</v>
       </c>
       <c r="O45">
-        <v>-0.917000532</v>
+        <v>-0.9518470559999996</v>
       </c>
       <c r="P45">
-        <v>-4.177446868</v>
+        <v>-4.336192143999998</v>
       </c>
       <c r="Q45">
-        <v>1.332553132</v>
+        <v>1.173807856000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1140858620665276</v>
+        <v>0.1153052524605728</v>
       </c>
       <c r="T45">
-        <v>1.151397735386682</v>
+        <v>1.171958409232873</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06984247386799514</v>
+        <v>0.06825514491644979</v>
       </c>
       <c r="W45">
-        <v>0.2193311446619268</v>
+        <v>0.2197054368287011</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3880137437110841</v>
+        <v>0.3791952495358323</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1612413335825493</v>
+        <v>0.1631413335825493</v>
       </c>
       <c r="C46">
-        <v>-4.107594918054303</v>
+        <v>-5.387881576698106</v>
       </c>
       <c r="D46">
-        <v>28.77640508194569</v>
+        <v>28.31711842330189</v>
       </c>
       <c r="E46">
-        <v>17.82399999999999</v>
+        <v>18.645</v>
       </c>
       <c r="F46">
-        <v>36.124</v>
+        <v>36.945</v>
       </c>
       <c r="G46">
         <v>3.24</v>
@@ -5047,37 +5047,37 @@
         <v>3.23</v>
       </c>
       <c r="M46">
-        <v>8.518039199999999</v>
+        <v>8.711631000000001</v>
       </c>
       <c r="N46">
-        <v>-5.288039199999998</v>
+        <v>-5.481631</v>
       </c>
       <c r="O46">
-        <v>-0.9518470559999996</v>
+        <v>-0.98669358</v>
       </c>
       <c r="P46">
-        <v>-4.336192143999998</v>
+        <v>-4.49493742</v>
       </c>
       <c r="Q46">
-        <v>1.173807856000002</v>
+        <v>1.015062579999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1153052524605728</v>
+        <v>0.1165689843234923</v>
       </c>
       <c r="T46">
-        <v>1.171958409232873</v>
+        <v>1.193266743946198</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06825514491644979</v>
+        <v>0.06673836391830647</v>
       </c>
       <c r="W46">
-        <v>0.2197054368287011</v>
+        <v>0.2200630937880634</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3791952495358323</v>
+        <v>0.3707686884350359</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1631413335825493</v>
+        <v>0.1650413335825493</v>
       </c>
       <c r="C47">
-        <v>-5.387881576698106</v>
+        <v>-6.653737638886049</v>
       </c>
       <c r="D47">
-        <v>28.31711842330189</v>
+        <v>27.87226236111395</v>
       </c>
       <c r="E47">
-        <v>18.645</v>
+        <v>19.466</v>
       </c>
       <c r="F47">
-        <v>36.945</v>
+        <v>37.766</v>
       </c>
       <c r="G47">
         <v>3.24</v>
@@ -5129,37 +5129,37 @@
         <v>3.23</v>
       </c>
       <c r="M47">
-        <v>8.711631000000001</v>
+        <v>8.905222800000001</v>
       </c>
       <c r="N47">
-        <v>-5.481631</v>
+        <v>-5.6752228</v>
       </c>
       <c r="O47">
-        <v>-0.98669358</v>
+        <v>-1.021540104</v>
       </c>
       <c r="P47">
-        <v>-4.49493742</v>
+        <v>-4.653682696000001</v>
       </c>
       <c r="Q47">
-        <v>1.015062579999999</v>
+        <v>0.8563173039999992</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1165689843234923</v>
+        <v>0.1178795210702236</v>
       </c>
       <c r="T47">
-        <v>1.193266743946198</v>
+        <v>1.215364276241498</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06673836391830647</v>
+        <v>0.06528752992008241</v>
       </c>
       <c r="W47">
-        <v>0.2200630937880634</v>
+        <v>0.2204052004448446</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3707686884350359</v>
+        <v>0.3627084995560134</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1650413335825493</v>
+        <v>0.1669413335825493</v>
       </c>
       <c r="C48">
-        <v>-6.653737638886049</v>
+        <v>-7.905832690600583</v>
       </c>
       <c r="D48">
-        <v>27.87226236111395</v>
+        <v>27.44116730939941</v>
       </c>
       <c r="E48">
-        <v>19.466</v>
+        <v>20.287</v>
       </c>
       <c r="F48">
-        <v>37.766</v>
+        <v>38.587</v>
       </c>
       <c r="G48">
         <v>3.24</v>
@@ -5211,37 +5211,37 @@
         <v>3.23</v>
       </c>
       <c r="M48">
-        <v>8.905222800000001</v>
+        <v>9.098814599999999</v>
       </c>
       <c r="N48">
-        <v>-5.6752228</v>
+        <v>-5.868814599999999</v>
       </c>
       <c r="O48">
-        <v>-1.021540104</v>
+        <v>-1.056386628</v>
       </c>
       <c r="P48">
-        <v>-4.653682696000001</v>
+        <v>-4.812427971999999</v>
       </c>
       <c r="Q48">
-        <v>0.8563173039999992</v>
+        <v>0.6975720280000006</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1178795210702236</v>
+        <v>0.1192395120338128</v>
       </c>
       <c r="T48">
-        <v>1.215364276241498</v>
+        <v>1.238295677680017</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06528752992008241</v>
+        <v>0.06389843353880406</v>
       </c>
       <c r="W48">
-        <v>0.2204052004448446</v>
+        <v>0.22073274937155</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3627084995560134</v>
+        <v>0.3549912974378004</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1669413335825493</v>
+        <v>0.1688413335825493</v>
       </c>
       <c r="C49">
-        <v>-7.905832690600583</v>
+        <v>-9.144795523341799</v>
       </c>
       <c r="D49">
-        <v>27.44116730939941</v>
+        <v>27.0232044766582</v>
       </c>
       <c r="E49">
-        <v>20.287</v>
+        <v>21.108</v>
       </c>
       <c r="F49">
-        <v>38.587</v>
+        <v>39.408</v>
       </c>
       <c r="G49">
         <v>3.24</v>
@@ -5293,37 +5293,37 @@
         <v>3.23</v>
       </c>
       <c r="M49">
-        <v>9.098814599999999</v>
+        <v>9.292406400000001</v>
       </c>
       <c r="N49">
-        <v>-5.868814599999999</v>
+        <v>-6.0624064</v>
       </c>
       <c r="O49">
-        <v>-1.056386628</v>
+        <v>-1.091233152</v>
       </c>
       <c r="P49">
-        <v>-4.812427971999999</v>
+        <v>-4.971173248</v>
       </c>
       <c r="Q49">
-        <v>0.6975720280000006</v>
+        <v>0.5388267519999994</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1192395120338128</v>
+        <v>0.1206518103421553</v>
       </c>
       <c r="T49">
-        <v>1.238295677680017</v>
+        <v>1.26210905609694</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06389843353880406</v>
+        <v>0.06256721617341231</v>
       </c>
       <c r="W49">
-        <v>0.22073274937155</v>
+        <v>0.2210466504263094</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3549912974378004</v>
+        <v>0.3475956454078462</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1688413335825492</v>
+        <v>0.1707413335825493</v>
       </c>
       <c r="C50">
-        <v>-9.144795523341784</v>
+        <v>-10.37121719426914</v>
       </c>
       <c r="D50">
-        <v>27.02320447665821</v>
+        <v>26.61778280573086</v>
       </c>
       <c r="E50">
-        <v>21.10799999999999</v>
+        <v>21.929</v>
       </c>
       <c r="F50">
-        <v>39.40799999999999</v>
+        <v>40.229</v>
       </c>
       <c r="G50">
         <v>3.24</v>
@@ -5375,37 +5375,37 @@
         <v>3.23</v>
       </c>
       <c r="M50">
-        <v>9.292406399999999</v>
+        <v>9.485998200000001</v>
       </c>
       <c r="N50">
-        <v>-6.062406399999999</v>
+        <v>-6.255998200000001</v>
       </c>
       <c r="O50">
-        <v>-1.091233152</v>
+        <v>-1.126079676</v>
       </c>
       <c r="P50">
-        <v>-4.971173247999999</v>
+        <v>-5.129918524000001</v>
       </c>
       <c r="Q50">
-        <v>0.5388267520000012</v>
+        <v>0.3800814759999991</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1206518103421553</v>
+        <v>0.1221194928978838</v>
       </c>
       <c r="T50">
-        <v>1.26210905609694</v>
+        <v>1.286856292490998</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06256721617341232</v>
+        <v>0.06129033421068961</v>
       </c>
       <c r="W50">
-        <v>0.2210466504263094</v>
+        <v>0.2213477391931194</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3475956454078463</v>
+        <v>0.3405018567260534</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1707413335825493</v>
+        <v>0.1726413335825492</v>
       </c>
       <c r="C51">
-        <v>-10.37121719426914</v>
+        <v>-11.58565381495203</v>
       </c>
       <c r="D51">
-        <v>26.61778280573086</v>
+        <v>26.22434618504796</v>
       </c>
       <c r="E51">
-        <v>21.929</v>
+        <v>22.75</v>
       </c>
       <c r="F51">
-        <v>40.229</v>
+        <v>41.05</v>
       </c>
       <c r="G51">
         <v>3.24</v>
@@ -5457,37 +5457,37 @@
         <v>3.23</v>
       </c>
       <c r="M51">
-        <v>9.485998200000001</v>
+        <v>9.679589999999999</v>
       </c>
       <c r="N51">
-        <v>-6.255998200000001</v>
+        <v>-6.449589999999999</v>
       </c>
       <c r="O51">
-        <v>-1.126079676</v>
+        <v>-1.1609262</v>
       </c>
       <c r="P51">
-        <v>-5.129918524000001</v>
+        <v>-5.288663799999999</v>
       </c>
       <c r="Q51">
-        <v>0.3800814759999991</v>
+        <v>0.2213362000000005</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1221194928978838</v>
+        <v>0.1236458827558415</v>
       </c>
       <c r="T51">
-        <v>1.286856292490998</v>
+        <v>1.312593418340818</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06129033421068961</v>
+        <v>0.06006452752647583</v>
       </c>
       <c r="W51">
-        <v>0.2213477391931194</v>
+        <v>0.221636784409257</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3405018567260534</v>
+        <v>0.3336918195915324</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1726413335825492</v>
+        <v>0.1745413335825493</v>
       </c>
       <c r="C52">
-        <v>-11.58565381495203</v>
+        <v>-12.78862909640024</v>
       </c>
       <c r="D52">
-        <v>26.22434618504796</v>
+        <v>25.84237090359976</v>
       </c>
       <c r="E52">
-        <v>22.75</v>
+        <v>23.57099999999999</v>
       </c>
       <c r="F52">
-        <v>41.05</v>
+        <v>41.871</v>
       </c>
       <c r="G52">
         <v>3.24</v>
@@ -5539,37 +5539,37 @@
         <v>3.23</v>
       </c>
       <c r="M52">
-        <v>9.679589999999999</v>
+        <v>9.873181799999999</v>
       </c>
       <c r="N52">
-        <v>-6.449589999999999</v>
+        <v>-6.643181799999999</v>
       </c>
       <c r="O52">
-        <v>-1.1609262</v>
+        <v>-1.195772724</v>
       </c>
       <c r="P52">
-        <v>-5.288663799999999</v>
+        <v>-5.447409076</v>
       </c>
       <c r="Q52">
-        <v>0.2213362000000005</v>
+        <v>0.06259092400000021</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1236458827558415</v>
+        <v>0.1252345742406546</v>
       </c>
       <c r="T52">
-        <v>1.312593418340818</v>
+        <v>1.339381039123284</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06006452752647583</v>
+        <v>0.05888679169262335</v>
       </c>
       <c r="W52">
-        <v>0.221636784409257</v>
+        <v>0.2219144945188794</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3336918195915324</v>
+        <v>0.3271488427367965</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1745413335825493</v>
+        <v>0.1764413335825493</v>
       </c>
       <c r="C53">
-        <v>-12.78862909640024</v>
+        <v>-13.98063667486696</v>
       </c>
       <c r="D53">
-        <v>25.84237090359976</v>
+        <v>25.47136332513304</v>
       </c>
       <c r="E53">
-        <v>23.57099999999999</v>
+        <v>24.392</v>
       </c>
       <c r="F53">
-        <v>41.871</v>
+        <v>42.692</v>
       </c>
       <c r="G53">
         <v>3.24</v>
@@ -5621,37 +5621,37 @@
         <v>3.23</v>
       </c>
       <c r="M53">
-        <v>9.873181799999999</v>
+        <v>10.0667736</v>
       </c>
       <c r="N53">
-        <v>-6.643181799999999</v>
+        <v>-6.836773600000001</v>
       </c>
       <c r="O53">
-        <v>-1.195772724</v>
+        <v>-1.230619248</v>
       </c>
       <c r="P53">
-        <v>-5.447409076</v>
+        <v>-5.606154352000001</v>
       </c>
       <c r="Q53">
-        <v>0.06259092400000021</v>
+        <v>-0.096154352000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1252345742406546</v>
+        <v>0.1268894612040015</v>
       </c>
       <c r="T53">
-        <v>1.339381039123284</v>
+        <v>1.367284810771686</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05888679169262335</v>
+        <v>0.05775435339084213</v>
       </c>
       <c r="W53">
-        <v>0.2219144945188794</v>
+        <v>0.2221815234704394</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3271488427367965</v>
+        <v>0.3208575188380118</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1764413335825493</v>
+        <v>0.1783413335825493</v>
       </c>
       <c r="C54">
-        <v>-13.98063667486696</v>
+        <v>-15.16214224014418</v>
       </c>
       <c r="D54">
-        <v>25.47136332513304</v>
+        <v>25.11085775985581</v>
       </c>
       <c r="E54">
-        <v>24.392</v>
+        <v>25.213</v>
       </c>
       <c r="F54">
-        <v>42.692</v>
+        <v>43.513</v>
       </c>
       <c r="G54">
         <v>3.24</v>
@@ -5703,37 +5703,37 @@
         <v>3.23</v>
       </c>
       <c r="M54">
-        <v>10.0667736</v>
+        <v>10.2603654</v>
       </c>
       <c r="N54">
-        <v>-6.836773600000001</v>
+        <v>-7.030365399999999</v>
       </c>
       <c r="O54">
-        <v>-1.230619248</v>
+        <v>-1.265465772</v>
       </c>
       <c r="P54">
-        <v>-5.606154352000001</v>
+        <v>-5.764899627999999</v>
       </c>
       <c r="Q54">
-        <v>-0.096154352000001</v>
+        <v>-0.2548996279999995</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1268894612040015</v>
+        <v>0.1286147688891931</v>
       </c>
       <c r="T54">
-        <v>1.367284810771686</v>
+        <v>1.396375976958317</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05775435339084213</v>
+        <v>0.05666464860988284</v>
       </c>
       <c r="W54">
-        <v>0.2221815234704394</v>
+        <v>0.2224384758577896</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3208575188380118</v>
+        <v>0.3148036033882381</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1783413335825493</v>
+        <v>0.1802413335825492</v>
       </c>
       <c r="C55">
-        <v>-15.16214224014418</v>
+        <v>-16.33358548564522</v>
       </c>
       <c r="D55">
-        <v>25.11085775985581</v>
+        <v>24.76041451435478</v>
       </c>
       <c r="E55">
-        <v>25.213</v>
+        <v>26.034</v>
       </c>
       <c r="F55">
-        <v>43.513</v>
+        <v>44.334</v>
       </c>
       <c r="G55">
         <v>3.24</v>
@@ -5785,37 +5785,37 @@
         <v>3.23</v>
       </c>
       <c r="M55">
-        <v>10.2603654</v>
+        <v>10.4539572</v>
       </c>
       <c r="N55">
-        <v>-7.030365399999999</v>
+        <v>-7.223957200000001</v>
       </c>
       <c r="O55">
-        <v>-1.265465772</v>
+        <v>-1.300312296</v>
       </c>
       <c r="P55">
-        <v>-5.764899627999999</v>
+        <v>-5.923644904000001</v>
       </c>
       <c r="Q55">
-        <v>-0.2548996279999995</v>
+        <v>-0.4136449040000008</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1286147688891931</v>
+        <v>0.1304150899520016</v>
       </c>
       <c r="T55">
-        <v>1.396375976958317</v>
+        <v>1.426731976457411</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05666464860988284</v>
+        <v>0.05561530326525538</v>
       </c>
       <c r="W55">
-        <v>0.2224384758577896</v>
+        <v>0.2226859114900528</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3148036033882381</v>
+        <v>0.3089739070291966</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1802413335825492</v>
+        <v>0.1821413335825493</v>
       </c>
       <c r="C56">
-        <v>-16.33358548564522</v>
+        <v>-17.4953818974443</v>
       </c>
       <c r="D56">
-        <v>24.76041451435478</v>
+        <v>24.4196181025557</v>
       </c>
       <c r="E56">
-        <v>26.034</v>
+        <v>26.855</v>
       </c>
       <c r="F56">
-        <v>44.334</v>
+        <v>45.155</v>
       </c>
       <c r="G56">
         <v>3.24</v>
@@ -5867,37 +5867,37 @@
         <v>3.23</v>
       </c>
       <c r="M56">
-        <v>10.4539572</v>
+        <v>10.647549</v>
       </c>
       <c r="N56">
-        <v>-7.223957200000001</v>
+        <v>-7.417549000000001</v>
       </c>
       <c r="O56">
-        <v>-1.300312296</v>
+        <v>-1.33515882</v>
       </c>
       <c r="P56">
-        <v>-5.923644904000001</v>
+        <v>-6.082390180000001</v>
       </c>
       <c r="Q56">
-        <v>-0.4136449040000008</v>
+        <v>-0.5723901800000011</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1304150899520016</v>
+        <v>0.1322954252842684</v>
       </c>
       <c r="T56">
-        <v>1.426731976457411</v>
+        <v>1.458437131489798</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05561530326525538</v>
+        <v>0.05460411593315983</v>
       </c>
       <c r="W56">
-        <v>0.2226859114900528</v>
+        <v>0.2229243494629609</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3089739070291966</v>
+        <v>0.3033561996286657</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1821413335825493</v>
+        <v>0.1840413335825493</v>
       </c>
       <c r="C57">
-        <v>-17.4953818974443</v>
+        <v>-18.64792439757856</v>
       </c>
       <c r="D57">
-        <v>24.4196181025557</v>
+        <v>24.08807560242144</v>
       </c>
       <c r="E57">
-        <v>26.855</v>
+        <v>27.676</v>
       </c>
       <c r="F57">
-        <v>45.155</v>
+        <v>45.976</v>
       </c>
       <c r="G57">
         <v>3.24</v>
@@ -5949,37 +5949,37 @@
         <v>3.23</v>
       </c>
       <c r="M57">
-        <v>10.647549</v>
+        <v>10.8411408</v>
       </c>
       <c r="N57">
-        <v>-7.417549000000001</v>
+        <v>-7.611140799999999</v>
       </c>
       <c r="O57">
-        <v>-1.33515882</v>
+        <v>-1.370005344</v>
       </c>
       <c r="P57">
-        <v>-6.082390180000001</v>
+        <v>-6.241135455999999</v>
       </c>
       <c r="Q57">
-        <v>-0.5723901800000011</v>
+        <v>-0.7311354559999996</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1322954252842684</v>
+        <v>0.1342612304043654</v>
       </c>
       <c r="T57">
-        <v>1.458437131489798</v>
+        <v>1.491583429932748</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05460411593315983</v>
+        <v>0.0536290424343534</v>
       </c>
       <c r="W57">
-        <v>0.2229243494629609</v>
+        <v>0.2231542717939795</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3033561996286657</v>
+        <v>0.2979391246352967</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1840413335825493</v>
+        <v>0.1859413335825493</v>
       </c>
       <c r="C58">
-        <v>-18.64792439757856</v>
+        <v>-19.79158485527775</v>
       </c>
       <c r="D58">
-        <v>24.08807560242144</v>
+        <v>23.76541514472225</v>
       </c>
       <c r="E58">
-        <v>27.676</v>
+        <v>28.497</v>
       </c>
       <c r="F58">
-        <v>45.976</v>
+        <v>46.797</v>
       </c>
       <c r="G58">
         <v>3.24</v>
@@ -6031,37 +6031,37 @@
         <v>3.23</v>
       </c>
       <c r="M58">
-        <v>10.8411408</v>
+        <v>11.0347326</v>
       </c>
       <c r="N58">
-        <v>-7.611140799999999</v>
+        <v>-7.804732600000001</v>
       </c>
       <c r="O58">
-        <v>-1.370005344</v>
+        <v>-1.404851868</v>
       </c>
       <c r="P58">
-        <v>-6.241135455999999</v>
+        <v>-6.399880732000002</v>
       </c>
       <c r="Q58">
-        <v>-0.7311354559999996</v>
+        <v>-0.8898807320000017</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1342612304043654</v>
+        <v>0.1363184683207459</v>
       </c>
       <c r="T58">
-        <v>1.491583429932748</v>
+        <v>1.52627141667537</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0536290424343534</v>
+        <v>0.05268818204076826</v>
       </c>
       <c r="W58">
-        <v>0.2231542717939795</v>
+        <v>0.2233761266747868</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2979391246352967</v>
+        <v>0.2927121224487125</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1859413335825493</v>
+        <v>0.1878413335825493</v>
       </c>
       <c r="C59">
-        <v>-19.79158485527775</v>
+        <v>-20.92671547834136</v>
       </c>
       <c r="D59">
-        <v>23.76541514472225</v>
+        <v>23.45128452165864</v>
       </c>
       <c r="E59">
-        <v>28.497</v>
+        <v>29.318</v>
       </c>
       <c r="F59">
-        <v>46.797</v>
+        <v>47.618</v>
       </c>
       <c r="G59">
         <v>3.24</v>
@@ -6113,37 +6113,37 @@
         <v>3.23</v>
       </c>
       <c r="M59">
-        <v>11.0347326</v>
+        <v>11.2283244</v>
       </c>
       <c r="N59">
-        <v>-7.804732600000001</v>
+        <v>-7.998324400000001</v>
       </c>
       <c r="O59">
-        <v>-1.404851868</v>
+        <v>-1.439698392</v>
       </c>
       <c r="P59">
-        <v>-6.399880732000002</v>
+        <v>-6.558626008000001</v>
       </c>
       <c r="Q59">
-        <v>-0.8898807320000017</v>
+        <v>-1.048626008000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1363184683207459</v>
+        <v>0.1384736699474304</v>
       </c>
       <c r="T59">
-        <v>1.52627141667537</v>
+        <v>1.562611212310498</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05268818204076826</v>
+        <v>0.05177976510903087</v>
       </c>
       <c r="W59">
-        <v>0.2233761266747868</v>
+        <v>0.2235903313872905</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2927121224487125</v>
+        <v>0.2876653617168382</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1878413335825492</v>
+        <v>0.1897413335825492</v>
       </c>
       <c r="C60">
-        <v>-20.92671547834136</v>
+        <v>-22.05365009560836</v>
       </c>
       <c r="D60">
-        <v>23.45128452165864</v>
+        <v>23.14534990439163</v>
       </c>
       <c r="E60">
-        <v>29.31799999999999</v>
+        <v>30.13899999999999</v>
       </c>
       <c r="F60">
-        <v>47.61799999999999</v>
+        <v>48.43899999999999</v>
       </c>
       <c r="G60">
         <v>3.24</v>
@@ -6195,37 +6195,37 @@
         <v>3.23</v>
       </c>
       <c r="M60">
-        <v>11.2283244</v>
+        <v>11.4219162</v>
       </c>
       <c r="N60">
-        <v>-7.9983244</v>
+        <v>-8.191916199999998</v>
       </c>
       <c r="O60">
-        <v>-1.439698392</v>
+        <v>-1.474544915999999</v>
       </c>
       <c r="P60">
-        <v>-6.558626007999999</v>
+        <v>-6.717371283999999</v>
       </c>
       <c r="Q60">
-        <v>-1.048626007999999</v>
+        <v>-1.207371283999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1384736699474304</v>
+        <v>0.1407340033607823</v>
       </c>
       <c r="T60">
-        <v>1.562611212310498</v>
+        <v>1.600723680903436</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05177976510903087</v>
+        <v>0.05090214197158968</v>
       </c>
       <c r="W60">
-        <v>0.2235903313872905</v>
+        <v>0.2237972749230991</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2876653617168382</v>
+        <v>0.2827896776199427</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1897413335825492</v>
+        <v>0.1916413335825493</v>
       </c>
       <c r="C61">
-        <v>-22.05365009560836</v>
+        <v>-23.17270534033644</v>
       </c>
       <c r="D61">
-        <v>23.14534990439163</v>
+        <v>22.84729465966356</v>
       </c>
       <c r="E61">
-        <v>30.13899999999999</v>
+        <v>30.96</v>
       </c>
       <c r="F61">
-        <v>48.43899999999999</v>
+        <v>49.26</v>
       </c>
       <c r="G61">
         <v>3.24</v>
@@ -6277,37 +6277,37 @@
         <v>3.23</v>
       </c>
       <c r="M61">
-        <v>11.4219162</v>
+        <v>11.615508</v>
       </c>
       <c r="N61">
-        <v>-8.191916199999998</v>
+        <v>-8.385508</v>
       </c>
       <c r="O61">
-        <v>-1.474544915999999</v>
+        <v>-1.50939144</v>
       </c>
       <c r="P61">
-        <v>-6.717371283999999</v>
+        <v>-6.87611656</v>
       </c>
       <c r="Q61">
-        <v>-1.207371283999999</v>
+        <v>-1.36611656</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1407340033607823</v>
+        <v>0.1431073534448019</v>
       </c>
       <c r="T61">
-        <v>1.600723680903436</v>
+        <v>1.640741772926023</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05090214197158968</v>
+        <v>0.05005377293872985</v>
       </c>
       <c r="W61">
-        <v>0.2237972749230991</v>
+        <v>0.2239973203410475</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2827896776199427</v>
+        <v>0.2780765163262769</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1916413335825493</v>
+        <v>0.1935413335825492</v>
       </c>
       <c r="C62">
-        <v>-23.17270534033644</v>
+        <v>-24.28418174330967</v>
       </c>
       <c r="D62">
-        <v>22.84729465966356</v>
+        <v>22.55681825669033</v>
       </c>
       <c r="E62">
-        <v>30.96</v>
+        <v>31.781</v>
       </c>
       <c r="F62">
-        <v>49.26</v>
+        <v>50.081</v>
       </c>
       <c r="G62">
         <v>3.24</v>
@@ -6359,37 +6359,37 @@
         <v>3.23</v>
       </c>
       <c r="M62">
-        <v>11.615508</v>
+        <v>11.8090998</v>
       </c>
       <c r="N62">
-        <v>-8.385508</v>
+        <v>-8.5790998</v>
       </c>
       <c r="O62">
-        <v>-1.50939144</v>
+        <v>-1.544237964</v>
       </c>
       <c r="P62">
-        <v>-6.87611656</v>
+        <v>-7.034861836</v>
       </c>
       <c r="Q62">
-        <v>-1.36611656</v>
+        <v>-1.524861836</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1431073534448019</v>
+        <v>0.1456024137895404</v>
       </c>
       <c r="T62">
-        <v>1.640741772926023</v>
+        <v>1.682812074795921</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05005377293872985</v>
+        <v>0.04923321928399657</v>
       </c>
       <c r="W62">
-        <v>0.2239973203410475</v>
+        <v>0.2241908068928336</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2780765163262769</v>
+        <v>0.2735178849110921</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1935413335825492</v>
+        <v>0.1954413335825493</v>
       </c>
       <c r="C63">
-        <v>-24.28418174330967</v>
+        <v>-25.3883647436076</v>
       </c>
       <c r="D63">
-        <v>22.55681825669033</v>
+        <v>22.27363525639239</v>
       </c>
       <c r="E63">
-        <v>31.781</v>
+        <v>32.60199999999999</v>
       </c>
       <c r="F63">
-        <v>50.081</v>
+        <v>50.90199999999999</v>
       </c>
       <c r="G63">
         <v>3.24</v>
@@ -6441,37 +6441,37 @@
         <v>3.23</v>
       </c>
       <c r="M63">
-        <v>11.8090998</v>
+        <v>12.0026916</v>
       </c>
       <c r="N63">
-        <v>-8.5790998</v>
+        <v>-8.772691599999998</v>
       </c>
       <c r="O63">
-        <v>-1.544237964</v>
+        <v>-1.579084488</v>
       </c>
       <c r="P63">
-        <v>-7.034861836</v>
+        <v>-7.193607111999999</v>
       </c>
       <c r="Q63">
-        <v>-1.524861836</v>
+        <v>-1.683607111999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1456024137895404</v>
+        <v>0.1482287930997915</v>
       </c>
       <c r="T63">
-        <v>1.682812074795921</v>
+        <v>1.727096603080024</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04923321928399657</v>
+        <v>0.04843913510199663</v>
       </c>
       <c r="W63">
-        <v>0.2241908068928336</v>
+        <v>0.2243780519429492</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2735178849110921</v>
+        <v>0.2691063061222035</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1954413335825493</v>
+        <v>0.1973413335825493</v>
       </c>
       <c r="C64">
-        <v>-25.3883647436076</v>
+        <v>-26.48552562418188</v>
       </c>
       <c r="D64">
-        <v>22.27363525639239</v>
+        <v>21.99747437581813</v>
       </c>
       <c r="E64">
-        <v>32.60199999999999</v>
+        <v>33.423</v>
       </c>
       <c r="F64">
-        <v>50.90199999999999</v>
+        <v>51.723</v>
       </c>
       <c r="G64">
         <v>3.24</v>
@@ -6523,37 +6523,37 @@
         <v>3.23</v>
       </c>
       <c r="M64">
-        <v>12.0026916</v>
+        <v>12.1962834</v>
       </c>
       <c r="N64">
-        <v>-8.772691599999998</v>
+        <v>-8.9662834</v>
       </c>
       <c r="O64">
-        <v>-1.579084488</v>
+        <v>-1.613931012</v>
       </c>
       <c r="P64">
-        <v>-7.193607111999999</v>
+        <v>-7.352352388</v>
       </c>
       <c r="Q64">
-        <v>-1.683607111999999</v>
+        <v>-1.842352388</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1482287930997915</v>
+        <v>0.1509971388592453</v>
       </c>
       <c r="T64">
-        <v>1.727096603080024</v>
+        <v>1.773774889649754</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04843913510199663</v>
+        <v>0.04767025994164747</v>
       </c>
       <c r="W64">
-        <v>0.2243780519429492</v>
+        <v>0.2245593527057596</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2691063061222035</v>
+        <v>0.2648347774535971</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1973413335825493</v>
+        <v>0.1992413335825493</v>
       </c>
       <c r="C65">
-        <v>-26.48552562418188</v>
+        <v>-27.57592237868631</v>
       </c>
       <c r="D65">
-        <v>21.99747437581813</v>
+        <v>21.72807762131368</v>
       </c>
       <c r="E65">
-        <v>33.423</v>
+        <v>34.244</v>
       </c>
       <c r="F65">
-        <v>51.723</v>
+        <v>52.544</v>
       </c>
       <c r="G65">
         <v>3.24</v>
@@ -6605,37 +6605,37 @@
         <v>3.23</v>
       </c>
       <c r="M65">
-        <v>12.1962834</v>
+        <v>12.3898752</v>
       </c>
       <c r="N65">
-        <v>-8.9662834</v>
+        <v>-9.1598752</v>
       </c>
       <c r="O65">
-        <v>-1.613931012</v>
+        <v>-1.648777536</v>
       </c>
       <c r="P65">
-        <v>-7.352352388</v>
+        <v>-7.511097664</v>
       </c>
       <c r="Q65">
-        <v>-1.842352388</v>
+        <v>-2.001097664</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1509971388592453</v>
+        <v>0.1539192816053354</v>
       </c>
       <c r="T65">
-        <v>1.773774889649754</v>
+        <v>1.823046414362247</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04767025994164747</v>
+        <v>0.04692541213005923</v>
       </c>
       <c r="W65">
-        <v>0.2245593527057596</v>
+        <v>0.2247349878197321</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2648347774535971</v>
+        <v>0.2606967340558847</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1992413335825493</v>
+        <v>0.2011413335825493</v>
       </c>
       <c r="C66">
-        <v>-27.57592237868631</v>
+        <v>-28.65980051538291</v>
       </c>
       <c r="D66">
-        <v>21.72807762131368</v>
+        <v>21.46519948461708</v>
       </c>
       <c r="E66">
-        <v>34.244</v>
+        <v>35.065</v>
       </c>
       <c r="F66">
-        <v>52.544</v>
+        <v>53.36499999999999</v>
       </c>
       <c r="G66">
         <v>3.24</v>
@@ -6687,37 +6687,37 @@
         <v>3.23</v>
       </c>
       <c r="M66">
-        <v>12.3898752</v>
+        <v>12.583467</v>
       </c>
       <c r="N66">
-        <v>-9.1598752</v>
+        <v>-9.353466999999998</v>
       </c>
       <c r="O66">
-        <v>-1.648777536</v>
+        <v>-1.68362406</v>
       </c>
       <c r="P66">
-        <v>-7.511097664</v>
+        <v>-7.669842939999999</v>
       </c>
       <c r="Q66">
-        <v>-2.001097664</v>
+        <v>-2.159842939999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1539192816053354</v>
+        <v>0.1570084039369164</v>
       </c>
       <c r="T66">
-        <v>1.823046414362247</v>
+        <v>1.875133454772598</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04692541213005923</v>
+        <v>0.04620348271267371</v>
       </c>
       <c r="W66">
-        <v>0.2247349878197321</v>
+        <v>0.2249052187763516</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2606967340558847</v>
+        <v>0.2566860150704096</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2011413335825493</v>
+        <v>0.2030413335825492</v>
       </c>
       <c r="C67">
-        <v>-28.65980051538291</v>
+        <v>-29.73739380338868</v>
       </c>
       <c r="D67">
-        <v>21.46519948461708</v>
+        <v>21.20860619661132</v>
       </c>
       <c r="E67">
-        <v>35.065</v>
+        <v>35.886</v>
       </c>
       <c r="F67">
-        <v>53.36499999999999</v>
+        <v>54.186</v>
       </c>
       <c r="G67">
         <v>3.24</v>
@@ -6769,37 +6769,37 @@
         <v>3.23</v>
       </c>
       <c r="M67">
-        <v>12.583467</v>
+        <v>12.7770588</v>
       </c>
       <c r="N67">
-        <v>-9.353466999999998</v>
+        <v>-9.5470588</v>
       </c>
       <c r="O67">
-        <v>-1.68362406</v>
+        <v>-1.718470584</v>
       </c>
       <c r="P67">
-        <v>-7.669842939999999</v>
+        <v>-7.828588216</v>
       </c>
       <c r="Q67">
-        <v>-2.159842939999999</v>
+        <v>-2.318588216</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1570084039369164</v>
+        <v>0.1602792393468257</v>
       </c>
       <c r="T67">
-        <v>1.875133454772598</v>
+        <v>1.930284438736497</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04620348271267371</v>
+        <v>0.04550342994429986</v>
       </c>
       <c r="W67">
-        <v>0.2249052187763516</v>
+        <v>0.2250702912191341</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2566860150704096</v>
+        <v>0.2527968330238881</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2030413335825492</v>
+        <v>0.2049413335825492</v>
       </c>
       <c r="C68">
-        <v>-29.73739380338868</v>
+        <v>-30.80892496603131</v>
       </c>
       <c r="D68">
-        <v>21.20860619661132</v>
+        <v>20.95807503396869</v>
       </c>
       <c r="E68">
-        <v>35.886</v>
+        <v>36.70699999999999</v>
       </c>
       <c r="F68">
-        <v>54.186</v>
+        <v>55.007</v>
       </c>
       <c r="G68">
         <v>3.24</v>
@@ -6851,37 +6851,37 @@
         <v>3.23</v>
       </c>
       <c r="M68">
-        <v>12.7770588</v>
+        <v>12.9706506</v>
       </c>
       <c r="N68">
-        <v>-9.5470588</v>
+        <v>-9.7406506</v>
       </c>
       <c r="O68">
-        <v>-1.718470584</v>
+        <v>-1.753317108</v>
       </c>
       <c r="P68">
-        <v>-7.828588216</v>
+        <v>-7.987333492</v>
       </c>
       <c r="Q68">
-        <v>-2.318588216</v>
+        <v>-2.477333492000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1602792393468257</v>
+        <v>0.1637483072058205</v>
       </c>
       <c r="T68">
-        <v>1.930284438736497</v>
+        <v>1.988777906576997</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04550342994429986</v>
+        <v>0.04482427427348942</v>
       </c>
       <c r="W68">
-        <v>0.2250702912191341</v>
+        <v>0.2252304361263112</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2527968330238881</v>
+        <v>0.24902374596383</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2049413335825492</v>
+        <v>0.2068413335825492</v>
       </c>
       <c r="C69">
-        <v>-30.80892496603131</v>
+        <v>-31.87460632563629</v>
       </c>
       <c r="D69">
-        <v>20.95807503396869</v>
+        <v>20.71339367436372</v>
       </c>
       <c r="E69">
-        <v>36.70699999999999</v>
+        <v>37.52800000000001</v>
       </c>
       <c r="F69">
-        <v>55.007</v>
+        <v>55.828</v>
       </c>
       <c r="G69">
         <v>3.24</v>
@@ -6933,37 +6933,37 @@
         <v>3.23</v>
       </c>
       <c r="M69">
-        <v>12.9706506</v>
+        <v>13.1642424</v>
       </c>
       <c r="N69">
-        <v>-9.7406506</v>
+        <v>-9.9342424</v>
       </c>
       <c r="O69">
-        <v>-1.753317108</v>
+        <v>-1.788163632</v>
       </c>
       <c r="P69">
-        <v>-7.987333492</v>
+        <v>-8.146078768000001</v>
       </c>
       <c r="Q69">
-        <v>-2.477333492000001</v>
+        <v>-2.636078768000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1637483072058205</v>
+        <v>0.1674341918060024</v>
       </c>
       <c r="T69">
-        <v>1.988777906576997</v>
+        <v>2.050927216157528</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04482427427348942</v>
+        <v>0.04416509376946751</v>
       </c>
       <c r="W69">
-        <v>0.2252304361263112</v>
+        <v>0.2253858708891596</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.24902374596383</v>
+        <v>0.2453616320525973</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2068413335825492</v>
+        <v>0.2087413335825493</v>
       </c>
       <c r="C70">
-        <v>-31.87460632563629</v>
+        <v>-32.93464040366834</v>
       </c>
       <c r="D70">
-        <v>20.71339367436372</v>
+        <v>20.47435959633166</v>
       </c>
       <c r="E70">
-        <v>37.52800000000001</v>
+        <v>38.349</v>
       </c>
       <c r="F70">
-        <v>55.828</v>
+        <v>56.649</v>
       </c>
       <c r="G70">
         <v>3.24</v>
@@ -7015,37 +7015,37 @@
         <v>3.23</v>
       </c>
       <c r="M70">
-        <v>13.1642424</v>
+        <v>13.3578342</v>
       </c>
       <c r="N70">
-        <v>-9.9342424</v>
+        <v>-10.1278342</v>
       </c>
       <c r="O70">
-        <v>-1.788163632</v>
+        <v>-1.823010156</v>
       </c>
       <c r="P70">
-        <v>-8.146078768000001</v>
+        <v>-8.304824044</v>
       </c>
       <c r="Q70">
-        <v>-2.636078768000001</v>
+        <v>-2.794824044</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1674341918060024</v>
+        <v>0.1713578754126476</v>
       </c>
       <c r="T70">
-        <v>2.050927216157528</v>
+        <v>2.117086158614223</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04416509376946751</v>
+        <v>0.0435250199467216</v>
       </c>
       <c r="W70">
-        <v>0.2253858708891596</v>
+        <v>0.225536800296563</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2453616320525973</v>
+        <v>0.2418056663706756</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2087413335825493</v>
+        <v>0.2106413335825493</v>
       </c>
       <c r="C71">
-        <v>-32.93464040366834</v>
+        <v>-33.98922047979324</v>
       </c>
       <c r="D71">
-        <v>20.47435959633166</v>
+        <v>20.24077952020676</v>
       </c>
       <c r="E71">
-        <v>38.349</v>
+        <v>39.17</v>
       </c>
       <c r="F71">
-        <v>56.649</v>
+        <v>57.47</v>
       </c>
       <c r="G71">
         <v>3.24</v>
@@ -7097,37 +7097,37 @@
         <v>3.23</v>
       </c>
       <c r="M71">
-        <v>13.3578342</v>
+        <v>13.551426</v>
       </c>
       <c r="N71">
-        <v>-10.1278342</v>
+        <v>-10.321426</v>
       </c>
       <c r="O71">
-        <v>-1.823010156</v>
+        <v>-1.85785668</v>
       </c>
       <c r="P71">
-        <v>-8.304824044</v>
+        <v>-8.463569320000001</v>
       </c>
       <c r="Q71">
-        <v>-2.794824044</v>
+        <v>-2.953569320000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1713578754126476</v>
+        <v>0.1755431379264025</v>
       </c>
       <c r="T71">
-        <v>2.117086158614223</v>
+        <v>2.187655697234697</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0435250199467216</v>
+        <v>0.04290323394748272</v>
       </c>
       <c r="W71">
-        <v>0.225536800296563</v>
+        <v>0.2256834174351836</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2418056663706756</v>
+        <v>0.2383512997082373</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2106413335825493</v>
+        <v>0.2125413335825493</v>
       </c>
       <c r="C72">
-        <v>-33.98922047979324</v>
+        <v>-35.03853111310292</v>
       </c>
       <c r="D72">
-        <v>20.24077952020676</v>
+        <v>20.01246888689709</v>
       </c>
       <c r="E72">
-        <v>39.17</v>
+        <v>39.991</v>
       </c>
       <c r="F72">
-        <v>57.47</v>
+        <v>58.291</v>
       </c>
       <c r="G72">
         <v>3.24</v>
@@ -7179,37 +7179,37 @@
         <v>3.23</v>
       </c>
       <c r="M72">
-        <v>13.551426</v>
+        <v>13.7450178</v>
       </c>
       <c r="N72">
-        <v>-10.321426</v>
+        <v>-10.5150178</v>
       </c>
       <c r="O72">
-        <v>-1.85785668</v>
+        <v>-1.892703204</v>
       </c>
       <c r="P72">
-        <v>-8.463569320000001</v>
+        <v>-8.622314596000001</v>
       </c>
       <c r="Q72">
-        <v>-2.953569320000001</v>
+        <v>-3.112314596000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1755431379264025</v>
+        <v>0.1800170392342095</v>
       </c>
       <c r="T72">
-        <v>2.187655697234697</v>
+        <v>2.263092100587618</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04290323394748272</v>
+        <v>0.04229896304681395</v>
       </c>
       <c r="W72">
-        <v>0.2256834174351836</v>
+        <v>0.2258259045135613</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2383512997082373</v>
+        <v>0.2349942391489664</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2125413335825493</v>
+        <v>0.2144413335825492</v>
       </c>
       <c r="C73">
-        <v>-35.03853111310291</v>
+        <v>-36.0827486284585</v>
       </c>
       <c r="D73">
-        <v>20.01246888689709</v>
+        <v>19.78925137154149</v>
       </c>
       <c r="E73">
-        <v>39.99099999999999</v>
+        <v>40.812</v>
       </c>
       <c r="F73">
-        <v>58.29099999999999</v>
+        <v>59.11199999999999</v>
       </c>
       <c r="G73">
         <v>3.24</v>
@@ -7261,37 +7261,37 @@
         <v>3.23</v>
       </c>
       <c r="M73">
-        <v>13.7450178</v>
+        <v>13.9386096</v>
       </c>
       <c r="N73">
-        <v>-10.5150178</v>
+        <v>-10.7086096</v>
       </c>
       <c r="O73">
-        <v>-1.892703203999999</v>
+        <v>-1.927549728</v>
       </c>
       <c r="P73">
-        <v>-8.622314595999997</v>
+        <v>-8.781059872</v>
       </c>
       <c r="Q73">
-        <v>-3.112314595999997</v>
+        <v>-3.271059872</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1800170392342095</v>
+        <v>0.1848105049211455</v>
       </c>
       <c r="T73">
-        <v>2.263092100587617</v>
+        <v>2.343916818465746</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04229896304681396</v>
+        <v>0.04171147744894154</v>
       </c>
       <c r="W73">
-        <v>0.2258259045135613</v>
+        <v>0.2259644336175396</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2349942391489664</v>
+        <v>0.2317304302718974</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2144413335825492</v>
+        <v>0.2163413335825493</v>
       </c>
       <c r="C74">
-        <v>-36.0827486284585</v>
+        <v>-37.1220415706446</v>
       </c>
       <c r="D74">
-        <v>19.78925137154149</v>
+        <v>19.57095842935539</v>
       </c>
       <c r="E74">
-        <v>40.812</v>
+        <v>41.633</v>
       </c>
       <c r="F74">
-        <v>59.11199999999999</v>
+        <v>59.93299999999999</v>
       </c>
       <c r="G74">
         <v>3.24</v>
@@ -7343,37 +7343,37 @@
         <v>3.23</v>
       </c>
       <c r="M74">
-        <v>13.9386096</v>
+        <v>14.1322014</v>
       </c>
       <c r="N74">
-        <v>-10.7086096</v>
+        <v>-10.9022014</v>
       </c>
       <c r="O74">
-        <v>-1.927549728</v>
+        <v>-1.962396252</v>
       </c>
       <c r="P74">
-        <v>-8.781059872</v>
+        <v>-8.939805148</v>
       </c>
       <c r="Q74">
-        <v>-3.271059872</v>
+        <v>-3.429805148</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1848105049211455</v>
+        <v>0.1899590421404472</v>
       </c>
       <c r="T74">
-        <v>2.343916818465746</v>
+        <v>2.430728552482996</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04171147744894154</v>
+        <v>0.04114008734690125</v>
       </c>
       <c r="W74">
-        <v>0.2259644336175396</v>
+        <v>0.2260991674036007</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2317304302718974</v>
+        <v>0.228556040816118</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2163413335825493</v>
+        <v>0.2182413335825493</v>
       </c>
       <c r="C75">
-        <v>-37.1220415706446</v>
+        <v>-38.15657112879305</v>
       </c>
       <c r="D75">
-        <v>19.57095842935539</v>
+        <v>19.35742887120695</v>
       </c>
       <c r="E75">
-        <v>41.633</v>
+        <v>42.45399999999999</v>
       </c>
       <c r="F75">
-        <v>59.93299999999999</v>
+        <v>60.754</v>
       </c>
       <c r="G75">
         <v>3.24</v>
@@ -7425,37 +7425,37 @@
         <v>3.23</v>
       </c>
       <c r="M75">
-        <v>14.1322014</v>
+        <v>14.3257932</v>
       </c>
       <c r="N75">
-        <v>-10.9022014</v>
+        <v>-11.0957932</v>
       </c>
       <c r="O75">
-        <v>-1.962396252</v>
+        <v>-1.997242776</v>
       </c>
       <c r="P75">
-        <v>-8.939805148</v>
+        <v>-9.098550423999999</v>
       </c>
       <c r="Q75">
-        <v>-3.429805148</v>
+        <v>-3.588550423999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1899590421404472</v>
+        <v>0.1955036206843106</v>
       </c>
       <c r="T75">
-        <v>2.430728552482996</v>
+        <v>2.524218112193881</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04114008734690125</v>
+        <v>0.04058414022059176</v>
       </c>
       <c r="W75">
-        <v>0.2260991674036007</v>
+        <v>0.2262302597359845</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.228556040816118</v>
+        <v>0.2254674456699542</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2182413335825493</v>
+        <v>0.2201413335825493</v>
       </c>
       <c r="C76">
-        <v>-38.15657112879305</v>
+        <v>-39.18649153332256</v>
       </c>
       <c r="D76">
-        <v>19.35742887120695</v>
+        <v>19.14850846667743</v>
       </c>
       <c r="E76">
-        <v>42.45399999999999</v>
+        <v>43.27499999999999</v>
       </c>
       <c r="F76">
-        <v>60.754</v>
+        <v>61.575</v>
       </c>
       <c r="G76">
         <v>3.24</v>
@@ -7507,37 +7507,37 @@
         <v>3.23</v>
       </c>
       <c r="M76">
-        <v>14.3257932</v>
+        <v>14.519385</v>
       </c>
       <c r="N76">
-        <v>-11.0957932</v>
+        <v>-11.289385</v>
       </c>
       <c r="O76">
-        <v>-1.997242776</v>
+        <v>-2.0320893</v>
       </c>
       <c r="P76">
-        <v>-9.098550423999999</v>
+        <v>-9.2572957</v>
       </c>
       <c r="Q76">
-        <v>-3.588550423999999</v>
+        <v>-3.7472957</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1955036206843106</v>
+        <v>0.201491765511683</v>
       </c>
       <c r="T76">
-        <v>2.524218112193881</v>
+        <v>2.625186836681636</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04058414022059176</v>
+        <v>0.04004301835098388</v>
       </c>
       <c r="W76">
-        <v>0.2262302597359845</v>
+        <v>0.226357856272838</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2254674456699542</v>
+        <v>0.2224612130610215</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2201413335825493</v>
+        <v>0.2220413335825493</v>
       </c>
       <c r="C77">
-        <v>-39.18649153332256</v>
+        <v>-40.21195042744831</v>
       </c>
       <c r="D77">
-        <v>19.14850846667743</v>
+        <v>18.94404957255168</v>
       </c>
       <c r="E77">
-        <v>43.27499999999999</v>
+        <v>44.09599999999999</v>
       </c>
       <c r="F77">
-        <v>61.575</v>
+        <v>62.39599999999999</v>
       </c>
       <c r="G77">
         <v>3.24</v>
@@ -7589,37 +7589,37 @@
         <v>3.23</v>
       </c>
       <c r="M77">
-        <v>14.519385</v>
+        <v>14.7129768</v>
       </c>
       <c r="N77">
-        <v>-11.289385</v>
+        <v>-11.4829768</v>
       </c>
       <c r="O77">
-        <v>-2.0320893</v>
+        <v>-2.066935824</v>
       </c>
       <c r="P77">
-        <v>-9.2572957</v>
+        <v>-9.416040976</v>
       </c>
       <c r="Q77">
-        <v>-3.7472957</v>
+        <v>-3.906040976</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.201491765511683</v>
+        <v>0.2079789224080031</v>
       </c>
       <c r="T77">
-        <v>2.625186836681636</v>
+        <v>2.734569621543371</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04004301835098388</v>
+        <v>0.03951613653057619</v>
       </c>
       <c r="W77">
-        <v>0.226357856272838</v>
+        <v>0.2264820950060902</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2224612130610215</v>
+        <v>0.2195340918365344</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2220413335825493</v>
+        <v>0.2239413335825493</v>
       </c>
       <c r="C78">
-        <v>-40.21195042744831</v>
+        <v>-41.23308921514203</v>
       </c>
       <c r="D78">
-        <v>18.94404957255168</v>
+        <v>18.74391078485797</v>
       </c>
       <c r="E78">
-        <v>44.09599999999999</v>
+        <v>44.917</v>
       </c>
       <c r="F78">
-        <v>62.39599999999999</v>
+        <v>63.217</v>
       </c>
       <c r="G78">
         <v>3.24</v>
@@ -7671,37 +7671,37 @@
         <v>3.23</v>
       </c>
       <c r="M78">
-        <v>14.7129768</v>
+        <v>14.9065686</v>
       </c>
       <c r="N78">
-        <v>-11.4829768</v>
+        <v>-11.6765686</v>
       </c>
       <c r="O78">
-        <v>-2.066935824</v>
+        <v>-2.101782348</v>
       </c>
       <c r="P78">
-        <v>-9.416040976</v>
+        <v>-9.574786251999999</v>
       </c>
       <c r="Q78">
-        <v>-3.906040976</v>
+        <v>-4.064786251999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2079789224080031</v>
+        <v>0.2150301799040033</v>
       </c>
       <c r="T78">
-        <v>2.734569621543371</v>
+        <v>2.853463952914822</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03951613653057619</v>
+        <v>0.03900293995225702</v>
       </c>
       <c r="W78">
-        <v>0.2264820950060902</v>
+        <v>0.2266031067592578</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2195340918365344</v>
+        <v>0.2166829997347612</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2239413335825493</v>
+        <v>0.2258413335825493</v>
       </c>
       <c r="C79">
-        <v>-41.23308921514203</v>
+        <v>-42.25004338726618</v>
       </c>
       <c r="D79">
-        <v>18.74391078485797</v>
+        <v>18.54795661273381</v>
       </c>
       <c r="E79">
-        <v>44.917</v>
+        <v>45.738</v>
       </c>
       <c r="F79">
-        <v>63.217</v>
+        <v>64.038</v>
       </c>
       <c r="G79">
         <v>3.24</v>
@@ -7753,37 +7753,37 @@
         <v>3.23</v>
       </c>
       <c r="M79">
-        <v>14.9065686</v>
+        <v>15.1001604</v>
       </c>
       <c r="N79">
-        <v>-11.6765686</v>
+        <v>-11.8701604</v>
       </c>
       <c r="O79">
-        <v>-2.101782348</v>
+        <v>-2.136628872</v>
       </c>
       <c r="P79">
-        <v>-9.574786251999999</v>
+        <v>-9.733531528</v>
       </c>
       <c r="Q79">
-        <v>-4.064786251999999</v>
+        <v>-4.223531528000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2150301799040033</v>
+        <v>0.2227224608087307</v>
       </c>
       <c r="T79">
-        <v>2.853463952914822</v>
+        <v>2.983166859865496</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03900293995225702</v>
+        <v>0.03850290226056142</v>
       </c>
       <c r="W79">
-        <v>0.2266031067592578</v>
+        <v>0.2267210156469596</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2166829997347612</v>
+        <v>0.2139050125586746</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2258413335825493</v>
+        <v>0.2277413335825493</v>
       </c>
       <c r="C80">
-        <v>-42.25004338726618</v>
+        <v>-43.26294282746272</v>
       </c>
       <c r="D80">
-        <v>18.54795661273381</v>
+        <v>18.35605717253727</v>
       </c>
       <c r="E80">
-        <v>45.738</v>
+        <v>46.559</v>
       </c>
       <c r="F80">
-        <v>64.038</v>
+        <v>64.85899999999999</v>
       </c>
       <c r="G80">
         <v>3.24</v>
@@ -7835,37 +7835,37 @@
         <v>3.23</v>
       </c>
       <c r="M80">
-        <v>15.1001604</v>
+        <v>15.2937522</v>
       </c>
       <c r="N80">
-        <v>-11.8701604</v>
+        <v>-12.0637522</v>
       </c>
       <c r="O80">
-        <v>-2.136628872</v>
+        <v>-2.171475396</v>
       </c>
       <c r="P80">
-        <v>-9.733531528</v>
+        <v>-9.892276804</v>
       </c>
       <c r="Q80">
-        <v>-4.223531528000001</v>
+        <v>-4.382276804</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2227224608087307</v>
+        <v>0.2311473398948607</v>
       </c>
       <c r="T80">
-        <v>2.983166859865496</v>
+        <v>3.125222424620996</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03850290226056142</v>
+        <v>0.03801552375093406</v>
       </c>
       <c r="W80">
-        <v>0.2267210156469596</v>
+        <v>0.2268359394995298</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2139050125586746</v>
+        <v>0.2111973541718559</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2277413335825493</v>
+        <v>0.2296413335825493</v>
       </c>
       <c r="C81">
-        <v>-43.26294282746272</v>
+        <v>-44.27191209924775</v>
       </c>
       <c r="D81">
-        <v>18.35605717253727</v>
+        <v>18.16808790075224</v>
       </c>
       <c r="E81">
-        <v>46.559</v>
+        <v>47.38</v>
       </c>
       <c r="F81">
-        <v>64.85899999999999</v>
+        <v>65.67999999999999</v>
       </c>
       <c r="G81">
         <v>3.24</v>
@@ -7917,37 +7917,37 @@
         <v>3.23</v>
       </c>
       <c r="M81">
-        <v>15.2937522</v>
+        <v>15.487344</v>
       </c>
       <c r="N81">
-        <v>-12.0637522</v>
+        <v>-12.257344</v>
       </c>
       <c r="O81">
-        <v>-2.171475396</v>
+        <v>-2.20632192</v>
       </c>
       <c r="P81">
-        <v>-9.892276804</v>
+        <v>-10.05102208</v>
       </c>
       <c r="Q81">
-        <v>-4.382276804</v>
+        <v>-4.541022079999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2311473398948607</v>
+        <v>0.2404147068896038</v>
       </c>
       <c r="T81">
-        <v>3.125222424620996</v>
+        <v>3.281483545852046</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03801552375093406</v>
+        <v>0.03754032970404739</v>
       </c>
       <c r="W81">
-        <v>0.2268359394995298</v>
+        <v>0.2269479902557856</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2111973541718559</v>
+        <v>0.2085573872447077</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2296413335825493</v>
+        <v>0.2315413335825492</v>
       </c>
       <c r="C82">
-        <v>-44.27191209924775</v>
+        <v>-45.27707071564557</v>
       </c>
       <c r="D82">
-        <v>18.16808790075224</v>
+        <v>17.98392928435443</v>
       </c>
       <c r="E82">
-        <v>47.38</v>
+        <v>48.20100000000001</v>
       </c>
       <c r="F82">
-        <v>65.67999999999999</v>
+        <v>66.501</v>
       </c>
       <c r="G82">
         <v>3.24</v>
@@ -7999,37 +7999,37 @@
         <v>3.23</v>
       </c>
       <c r="M82">
-        <v>15.487344</v>
+        <v>15.6809358</v>
       </c>
       <c r="N82">
-        <v>-12.257344</v>
+        <v>-12.4509358</v>
       </c>
       <c r="O82">
-        <v>-2.20632192</v>
+        <v>-2.241168444</v>
       </c>
       <c r="P82">
-        <v>-10.05102208</v>
+        <v>-10.209767356</v>
       </c>
       <c r="Q82">
-        <v>-4.541022079999999</v>
+        <v>-4.699767356000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2404147068896038</v>
+        <v>0.2506575861995829</v>
       </c>
       <c r="T82">
-        <v>3.281483545852046</v>
+        <v>3.454193206160048</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03754032970404739</v>
+        <v>0.03707686884350359</v>
       </c>
       <c r="W82">
-        <v>0.2269479902557856</v>
+        <v>0.2270572743267019</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2085573872447077</v>
+        <v>0.2059826046861311</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2315413335825492</v>
+        <v>0.2334413335825493</v>
       </c>
       <c r="C83">
-        <v>-45.27707071564557</v>
+        <v>-46.27853339258857</v>
       </c>
       <c r="D83">
-        <v>17.98392928435443</v>
+        <v>17.80346660741143</v>
       </c>
       <c r="E83">
-        <v>48.20100000000001</v>
+        <v>49.02200000000001</v>
       </c>
       <c r="F83">
-        <v>66.501</v>
+        <v>67.322</v>
       </c>
       <c r="G83">
         <v>3.24</v>
@@ -8081,37 +8081,37 @@
         <v>3.23</v>
       </c>
       <c r="M83">
-        <v>15.6809358</v>
+        <v>15.8745276</v>
       </c>
       <c r="N83">
-        <v>-12.4509358</v>
+        <v>-12.6445276</v>
       </c>
       <c r="O83">
-        <v>-2.241168444</v>
+        <v>-2.276014968</v>
       </c>
       <c r="P83">
-        <v>-10.209767356</v>
+        <v>-10.368512632</v>
       </c>
       <c r="Q83">
-        <v>-4.699767356000001</v>
+        <v>-4.858512632</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2506575861995829</v>
+        <v>0.2620385632106709</v>
       </c>
       <c r="T83">
-        <v>3.454193206160048</v>
+        <v>3.646092828724496</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03707686884350359</v>
+        <v>0.03662471190638769</v>
       </c>
       <c r="W83">
-        <v>0.2270572743267019</v>
+        <v>0.2271638929324738</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2059826046861311</v>
+        <v>0.2034706217021539</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2334413335825493</v>
+        <v>0.2353413335825493</v>
       </c>
       <c r="C84">
-        <v>-46.27853339258857</v>
+        <v>-47.2764102872121</v>
       </c>
       <c r="D84">
-        <v>17.80346660741143</v>
+        <v>17.6265897127879</v>
       </c>
       <c r="E84">
-        <v>49.02200000000001</v>
+        <v>49.843</v>
       </c>
       <c r="F84">
-        <v>67.322</v>
+        <v>68.143</v>
       </c>
       <c r="G84">
         <v>3.24</v>
@@ -8163,37 +8163,37 @@
         <v>3.23</v>
       </c>
       <c r="M84">
-        <v>15.8745276</v>
+        <v>16.0681194</v>
       </c>
       <c r="N84">
-        <v>-12.6445276</v>
+        <v>-12.8381194</v>
       </c>
       <c r="O84">
-        <v>-2.276014968</v>
+        <v>-2.310861492</v>
       </c>
       <c r="P84">
-        <v>-10.368512632</v>
+        <v>-10.527257908</v>
       </c>
       <c r="Q84">
-        <v>-4.858512632</v>
+        <v>-5.017257907999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2620385632106709</v>
+        <v>0.2747584786936516</v>
       </c>
       <c r="T84">
-        <v>3.646092828724496</v>
+        <v>3.860568877472996</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03662471190638769</v>
+        <v>0.03618345031715411</v>
       </c>
       <c r="W84">
-        <v>0.2271638929324738</v>
+        <v>0.2272679424152151</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2034706217021539</v>
+        <v>0.2010191684286339</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2353413335825493</v>
+        <v>0.2372413335825493</v>
       </c>
       <c r="C85">
-        <v>-47.2764102872121</v>
+        <v>-48.27080722208422</v>
       </c>
       <c r="D85">
-        <v>17.6265897127879</v>
+        <v>17.45319277791577</v>
       </c>
       <c r="E85">
-        <v>49.843</v>
+        <v>50.664</v>
       </c>
       <c r="F85">
-        <v>68.143</v>
+        <v>68.964</v>
       </c>
       <c r="G85">
         <v>3.24</v>
@@ -8245,37 +8245,37 @@
         <v>3.23</v>
       </c>
       <c r="M85">
-        <v>16.0681194</v>
+        <v>16.2617112</v>
       </c>
       <c r="N85">
-        <v>-12.8381194</v>
+        <v>-13.0317112</v>
       </c>
       <c r="O85">
-        <v>-2.310861492</v>
+        <v>-2.345708016</v>
       </c>
       <c r="P85">
-        <v>-10.527257908</v>
+        <v>-10.686003184</v>
       </c>
       <c r="Q85">
-        <v>-5.017257907999999</v>
+        <v>-5.176003184000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2747584786936516</v>
+        <v>0.2890683836120048</v>
       </c>
       <c r="T85">
-        <v>3.860568877472996</v>
+        <v>4.101854432315059</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03618345031715411</v>
+        <v>0.03575269495623561</v>
       </c>
       <c r="W85">
-        <v>0.2272679424152151</v>
+        <v>0.2273695145293197</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2010191684286339</v>
+        <v>0.1986260830901978</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2372413335825493</v>
+        <v>0.2391413335825493</v>
       </c>
       <c r="C86">
-        <v>-48.27080722208422</v>
+        <v>-49.26182589632973</v>
       </c>
       <c r="D86">
-        <v>17.45319277791577</v>
+        <v>17.28317410367026</v>
       </c>
       <c r="E86">
-        <v>50.664</v>
+        <v>51.485</v>
       </c>
       <c r="F86">
-        <v>68.964</v>
+        <v>69.785</v>
       </c>
       <c r="G86">
         <v>3.24</v>
@@ -8327,37 +8327,37 @@
         <v>3.23</v>
       </c>
       <c r="M86">
-        <v>16.2617112</v>
+        <v>16.455303</v>
       </c>
       <c r="N86">
-        <v>-13.0317112</v>
+        <v>-13.225303</v>
       </c>
       <c r="O86">
-        <v>-2.345708016</v>
+        <v>-2.38055454</v>
       </c>
       <c r="P86">
-        <v>-10.686003184</v>
+        <v>-10.84474846</v>
       </c>
       <c r="Q86">
-        <v>-5.176003184000001</v>
+        <v>-5.33474846</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2890683836120047</v>
+        <v>0.3052862758528049</v>
       </c>
       <c r="T86">
-        <v>4.101854432315056</v>
+        <v>4.375311394469393</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03575269495623561</v>
+        <v>0.03533207501557401</v>
       </c>
       <c r="W86">
-        <v>0.2273695145293197</v>
+        <v>0.2274686967113277</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1986260830901978</v>
+        <v>0.1962893056420778</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2391413335825493</v>
+        <v>0.2410413335825493</v>
       </c>
       <c r="C87">
-        <v>-49.26182589632973</v>
+        <v>-50.24956408453322</v>
       </c>
       <c r="D87">
-        <v>17.28317410367026</v>
+        <v>17.11643591546677</v>
       </c>
       <c r="E87">
-        <v>51.485</v>
+        <v>52.306</v>
       </c>
       <c r="F87">
-        <v>69.785</v>
+        <v>70.60599999999999</v>
       </c>
       <c r="G87">
         <v>3.24</v>
@@ -8409,37 +8409,37 @@
         <v>3.23</v>
       </c>
       <c r="M87">
-        <v>16.455303</v>
+        <v>16.6488948</v>
       </c>
       <c r="N87">
-        <v>-13.225303</v>
+        <v>-13.4188948</v>
       </c>
       <c r="O87">
-        <v>-2.38055454</v>
+        <v>-2.415401064</v>
       </c>
       <c r="P87">
-        <v>-10.84474846</v>
+        <v>-11.003493736</v>
       </c>
       <c r="Q87">
-        <v>-5.33474846</v>
+        <v>-5.493493736</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3052862758528049</v>
+        <v>0.3238210098422911</v>
       </c>
       <c r="T87">
-        <v>4.375311394469393</v>
+        <v>4.687833636931493</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03533207501557401</v>
+        <v>0.03492123693399757</v>
       </c>
       <c r="W87">
-        <v>0.2274686967113277</v>
+        <v>0.2275655723309634</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1962893056420778</v>
+        <v>0.194006871855542</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2410413335825493</v>
+        <v>0.2429413335825493</v>
       </c>
       <c r="C88">
-        <v>-50.24956408453322</v>
+        <v>-51.23411582423882</v>
       </c>
       <c r="D88">
-        <v>17.11643591546677</v>
+        <v>16.95288417576117</v>
       </c>
       <c r="E88">
-        <v>52.306</v>
+        <v>53.127</v>
       </c>
       <c r="F88">
-        <v>70.60599999999999</v>
+        <v>71.42699999999999</v>
       </c>
       <c r="G88">
         <v>3.24</v>
@@ -8491,37 +8491,37 @@
         <v>3.23</v>
       </c>
       <c r="M88">
-        <v>16.6488948</v>
+        <v>16.8424866</v>
       </c>
       <c r="N88">
-        <v>-13.4188948</v>
+        <v>-13.6124866</v>
       </c>
       <c r="O88">
-        <v>-2.415401064</v>
+        <v>-2.450247587999999</v>
       </c>
       <c r="P88">
-        <v>-11.003493736</v>
+        <v>-11.162239012</v>
       </c>
       <c r="Q88">
-        <v>-5.493493736</v>
+        <v>-5.652239011999997</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3238210098422911</v>
+        <v>0.3452072413686211</v>
       </c>
       <c r="T88">
-        <v>4.687833636931493</v>
+        <v>5.048436224387761</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03492123693399757</v>
+        <v>0.03451984340602059</v>
       </c>
       <c r="W88">
-        <v>0.2275655723309634</v>
+        <v>0.2276602209248604</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.194006871855542</v>
+        <v>0.1917769078112255</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2429413335825493</v>
+        <v>0.2448413335825493</v>
       </c>
       <c r="C89">
-        <v>-51.23411582423882</v>
+        <v>-52.21557159280202</v>
       </c>
       <c r="D89">
-        <v>16.95288417576117</v>
+        <v>16.79242840719797</v>
       </c>
       <c r="E89">
-        <v>53.127</v>
+        <v>53.94799999999999</v>
       </c>
       <c r="F89">
-        <v>71.42699999999999</v>
+        <v>72.24799999999999</v>
       </c>
       <c r="G89">
         <v>3.24</v>
@@ -8573,37 +8573,37 @@
         <v>3.23</v>
       </c>
       <c r="M89">
-        <v>16.8424866</v>
+        <v>17.0360784</v>
       </c>
       <c r="N89">
-        <v>-13.6124866</v>
+        <v>-13.8060784</v>
       </c>
       <c r="O89">
-        <v>-2.450247587999999</v>
+        <v>-2.485094111999999</v>
       </c>
       <c r="P89">
-        <v>-11.162239012</v>
+        <v>-11.320984288</v>
       </c>
       <c r="Q89">
-        <v>-5.652239011999997</v>
+        <v>-5.810984287999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3452072413686211</v>
+        <v>0.3701578448160062</v>
       </c>
       <c r="T89">
-        <v>5.048436224387761</v>
+        <v>5.469139243086742</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03451984340602059</v>
+        <v>0.0341275724582249</v>
       </c>
       <c r="W89">
-        <v>0.2276602209248604</v>
+        <v>0.2277527184143506</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1917769078112255</v>
+        <v>0.1895976247679161</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2448413335825493</v>
+        <v>0.2467413335825493</v>
       </c>
       <c r="C90">
-        <v>-52.21557159280202</v>
+        <v>-53.19401847429246</v>
       </c>
       <c r="D90">
-        <v>16.79242840719797</v>
+        <v>16.63498152570754</v>
       </c>
       <c r="E90">
-        <v>53.94799999999999</v>
+        <v>54.76900000000001</v>
       </c>
       <c r="F90">
-        <v>72.24799999999999</v>
+        <v>73.069</v>
       </c>
       <c r="G90">
         <v>3.24</v>
@@ -8655,37 +8655,37 @@
         <v>3.23</v>
       </c>
       <c r="M90">
-        <v>17.0360784</v>
+        <v>17.2296702</v>
       </c>
       <c r="N90">
-        <v>-13.8060784</v>
+        <v>-13.9996702</v>
       </c>
       <c r="O90">
-        <v>-2.485094111999999</v>
+        <v>-2.519940636</v>
       </c>
       <c r="P90">
-        <v>-11.320984288</v>
+        <v>-11.479729564</v>
       </c>
       <c r="Q90">
-        <v>-5.810984287999998</v>
+        <v>-5.969729564000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3701578448160062</v>
+        <v>0.3996449216174614</v>
       </c>
       <c r="T90">
-        <v>5.469139243086742</v>
+        <v>5.966333719730992</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0341275724582249</v>
+        <v>0.03374411658790776</v>
       </c>
       <c r="W90">
-        <v>0.2277527184143506</v>
+        <v>0.2278431373085714</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1895976247679161</v>
+        <v>0.1874673143772654</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2467413335825493</v>
+        <v>0.2486413335825493</v>
       </c>
       <c r="C91">
-        <v>-53.19401847429246</v>
+        <v>-54.16954031709454</v>
       </c>
       <c r="D91">
-        <v>16.63498152570754</v>
+        <v>16.48045968290547</v>
       </c>
       <c r="E91">
-        <v>54.76900000000001</v>
+        <v>55.59</v>
       </c>
       <c r="F91">
-        <v>73.069</v>
+        <v>73.89</v>
       </c>
       <c r="G91">
         <v>3.24</v>
@@ -8737,37 +8737,37 @@
         <v>3.23</v>
       </c>
       <c r="M91">
-        <v>17.2296702</v>
+        <v>17.423262</v>
       </c>
       <c r="N91">
-        <v>-13.9996702</v>
+        <v>-14.193262</v>
       </c>
       <c r="O91">
-        <v>-2.519940636</v>
+        <v>-2.55478716</v>
       </c>
       <c r="P91">
-        <v>-11.479729564</v>
+        <v>-11.63847484</v>
       </c>
       <c r="Q91">
-        <v>-5.969729564000001</v>
+        <v>-6.128474840000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3996449216174614</v>
+        <v>0.4350294137792075</v>
       </c>
       <c r="T91">
-        <v>5.966333719730992</v>
+        <v>6.562967091704091</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03374411658790776</v>
+        <v>0.03336918195915323</v>
       </c>
       <c r="W91">
-        <v>0.2278431373085714</v>
+        <v>0.2279315468940317</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1874673143772654</v>
+        <v>0.1853843442175179</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2486413335825493</v>
+        <v>0.2505413335825493</v>
       </c>
       <c r="C92">
-        <v>-54.16954031709454</v>
+        <v>-55.14221788280528</v>
       </c>
       <c r="D92">
-        <v>16.48045968290547</v>
+        <v>16.32878211719471</v>
       </c>
       <c r="E92">
-        <v>55.59</v>
+        <v>56.411</v>
       </c>
       <c r="F92">
-        <v>73.89</v>
+        <v>74.711</v>
       </c>
       <c r="G92">
         <v>3.24</v>
@@ -8819,37 +8819,37 @@
         <v>3.23</v>
       </c>
       <c r="M92">
-        <v>17.423262</v>
+        <v>17.6168538</v>
       </c>
       <c r="N92">
-        <v>-14.193262</v>
+        <v>-14.3868538</v>
       </c>
       <c r="O92">
-        <v>-2.55478716</v>
+        <v>-2.589633684</v>
       </c>
       <c r="P92">
-        <v>-11.63847484</v>
+        <v>-11.797220116</v>
       </c>
       <c r="Q92">
-        <v>-6.128474840000001</v>
+        <v>-6.287220116</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4350294137792075</v>
+        <v>0.4782771264213417</v>
       </c>
       <c r="T92">
-        <v>6.562967091704091</v>
+        <v>7.292185657448991</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03336918195915323</v>
+        <v>0.03300248765190979</v>
       </c>
       <c r="W92">
-        <v>0.2279315468940317</v>
+        <v>0.2280180134116797</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1853843442175179</v>
+        <v>0.183347153621721</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2505413335825493</v>
+        <v>0.2524413335825493</v>
       </c>
       <c r="C93">
-        <v>-55.14221788280528</v>
+        <v>-56.11212898698484</v>
       </c>
       <c r="D93">
-        <v>16.32878211719471</v>
+        <v>16.17987101301516</v>
       </c>
       <c r="E93">
-        <v>56.411</v>
+        <v>57.232</v>
       </c>
       <c r="F93">
-        <v>74.711</v>
+        <v>75.532</v>
       </c>
       <c r="G93">
         <v>3.24</v>
@@ -8901,37 +8901,37 @@
         <v>3.23</v>
       </c>
       <c r="M93">
-        <v>17.6168538</v>
+        <v>17.8104456</v>
       </c>
       <c r="N93">
-        <v>-14.3868538</v>
+        <v>-14.5804456</v>
       </c>
       <c r="O93">
-        <v>-2.589633684</v>
+        <v>-2.624480208</v>
       </c>
       <c r="P93">
-        <v>-11.797220116</v>
+        <v>-11.955965392</v>
       </c>
       <c r="Q93">
-        <v>-6.287220116</v>
+        <v>-6.445965392000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4782771264213417</v>
+        <v>0.5323367672240096</v>
       </c>
       <c r="T93">
-        <v>7.292185657448991</v>
+        <v>8.203708864630118</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03300248765190979</v>
+        <v>0.0326437649600412</v>
       </c>
       <c r="W93">
-        <v>0.2280180134116797</v>
+        <v>0.2281026002224223</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.183347153621721</v>
+        <v>0.1813542497780067</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2524413335825493</v>
+        <v>0.2543413335825492</v>
       </c>
       <c r="C94">
-        <v>-56.11212898698484</v>
+        <v>-57.07934863227507</v>
       </c>
       <c r="D94">
-        <v>16.17987101301516</v>
+        <v>16.03365136772492</v>
       </c>
       <c r="E94">
-        <v>57.232</v>
+        <v>58.053</v>
       </c>
       <c r="F94">
-        <v>75.532</v>
+        <v>76.35299999999999</v>
       </c>
       <c r="G94">
         <v>3.24</v>
@@ -8983,37 +8983,37 @@
         <v>3.23</v>
       </c>
       <c r="M94">
-        <v>17.8104456</v>
+        <v>18.0040374</v>
       </c>
       <c r="N94">
-        <v>-14.5804456</v>
+        <v>-14.7740374</v>
       </c>
       <c r="O94">
-        <v>-2.624480208</v>
+        <v>-2.659326731999999</v>
       </c>
       <c r="P94">
-        <v>-11.955965392</v>
+        <v>-12.114710668</v>
       </c>
       <c r="Q94">
-        <v>-6.445965392000002</v>
+        <v>-6.604710667999997</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5323367672240096</v>
+        <v>0.6018420196845824</v>
       </c>
       <c r="T94">
-        <v>8.203708864630118</v>
+        <v>9.375667273862993</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0326437649600412</v>
+        <v>0.03229275673466442</v>
       </c>
       <c r="W94">
-        <v>0.2281026002224223</v>
+        <v>0.2281853679619661</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1813542497780067</v>
+        <v>0.1794042040814691</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2543413335825492</v>
+        <v>0.2562413335825493</v>
       </c>
       <c r="C95">
-        <v>-57.07934863227507</v>
+        <v>-58.04394913436487</v>
       </c>
       <c r="D95">
-        <v>16.03365136772492</v>
+        <v>15.89005086563512</v>
       </c>
       <c r="E95">
-        <v>58.053</v>
+        <v>58.874</v>
       </c>
       <c r="F95">
-        <v>76.35299999999999</v>
+        <v>77.17399999999999</v>
       </c>
       <c r="G95">
         <v>3.24</v>
@@ -9065,37 +9065,37 @@
         <v>3.23</v>
       </c>
       <c r="M95">
-        <v>18.0040374</v>
+        <v>18.1976292</v>
       </c>
       <c r="N95">
-        <v>-14.7740374</v>
+        <v>-14.9676292</v>
       </c>
       <c r="O95">
-        <v>-2.659326731999999</v>
+        <v>-2.694173256</v>
       </c>
       <c r="P95">
-        <v>-12.114710668</v>
+        <v>-12.273455944</v>
       </c>
       <c r="Q95">
-        <v>-6.604710667999997</v>
+        <v>-6.763455943999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6018420196845824</v>
+        <v>0.6945156896320129</v>
       </c>
       <c r="T95">
-        <v>9.375667273862993</v>
+        <v>10.93827848617349</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03229275673466442</v>
+        <v>0.03194921676940203</v>
       </c>
       <c r="W95">
-        <v>0.2281853679619661</v>
+        <v>0.228266374685775</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1794042040814691</v>
+        <v>0.1774956487189002</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2562413335825493</v>
+        <v>0.2581413335825493</v>
       </c>
       <c r="C96">
-        <v>-58.04394913436487</v>
+        <v>-59.00600024124634</v>
       </c>
       <c r="D96">
-        <v>15.89005086563512</v>
+        <v>15.74899975875366</v>
       </c>
       <c r="E96">
-        <v>58.874</v>
+        <v>59.69500000000001</v>
       </c>
       <c r="F96">
-        <v>77.17399999999999</v>
+        <v>77.995</v>
       </c>
       <c r="G96">
         <v>3.24</v>
@@ -9147,37 +9147,37 @@
         <v>3.23</v>
       </c>
       <c r="M96">
-        <v>18.1976292</v>
+        <v>18.391221</v>
       </c>
       <c r="N96">
-        <v>-14.9676292</v>
+        <v>-15.161221</v>
       </c>
       <c r="O96">
-        <v>-2.694173256</v>
+        <v>-2.72901978</v>
       </c>
       <c r="P96">
-        <v>-12.273455944</v>
+        <v>-12.43220122</v>
       </c>
       <c r="Q96">
-        <v>-6.763455943999999</v>
+        <v>-6.922201220000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6945156896320129</v>
+        <v>0.8242588275584162</v>
       </c>
       <c r="T96">
-        <v>10.93827848617349</v>
+        <v>13.1259341834082</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03194921676940203</v>
+        <v>0.03161290922446095</v>
       </c>
       <c r="W96">
-        <v>0.228266374685775</v>
+        <v>0.2283456760048721</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1774956487189002</v>
+        <v>0.1756272734692276</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2581413335825493</v>
+        <v>0.2600413335825493</v>
       </c>
       <c r="C97">
-        <v>-59.00600024124634</v>
+        <v>-59.96556924617541</v>
       </c>
       <c r="D97">
-        <v>15.74899975875366</v>
+        <v>15.61043075382459</v>
       </c>
       <c r="E97">
-        <v>59.69500000000001</v>
+        <v>60.51600000000001</v>
       </c>
       <c r="F97">
-        <v>77.995</v>
+        <v>78.816</v>
       </c>
       <c r="G97">
         <v>3.24</v>
@@ -9229,37 +9229,37 @@
         <v>3.23</v>
       </c>
       <c r="M97">
-        <v>18.391221</v>
+        <v>18.5848128</v>
       </c>
       <c r="N97">
-        <v>-15.161221</v>
+        <v>-15.3548128</v>
       </c>
       <c r="O97">
-        <v>-2.72901978</v>
+        <v>-2.763866304</v>
       </c>
       <c r="P97">
-        <v>-12.43220122</v>
+        <v>-12.590946496</v>
       </c>
       <c r="Q97">
-        <v>-6.922201220000002</v>
+        <v>-7.080946496000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8242588275584162</v>
+        <v>1.01887353444802</v>
       </c>
       <c r="T97">
-        <v>13.1259341834082</v>
+        <v>16.40741772926026</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03161290922446095</v>
+        <v>0.03128360808670615</v>
       </c>
       <c r="W97">
-        <v>0.2283456760048721</v>
+        <v>0.2284233252131547</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1756272734692276</v>
+        <v>0.1737978227039231</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2600413335825493</v>
+        <v>0.2619413335825492</v>
       </c>
       <c r="C98">
-        <v>-59.9655692461754</v>
+        <v>-60.92272109472105</v>
       </c>
       <c r="D98">
-        <v>15.61043075382459</v>
+        <v>15.47427890527894</v>
       </c>
       <c r="E98">
-        <v>60.51599999999999</v>
+        <v>61.33699999999999</v>
       </c>
       <c r="F98">
-        <v>78.81599999999999</v>
+        <v>79.63699999999999</v>
       </c>
       <c r="G98">
         <v>3.24</v>
@@ -9311,37 +9311,37 @@
         <v>3.23</v>
       </c>
       <c r="M98">
-        <v>18.5848128</v>
+        <v>18.7784046</v>
       </c>
       <c r="N98">
-        <v>-15.3548128</v>
+        <v>-15.5484046</v>
       </c>
       <c r="O98">
-        <v>-2.763866304</v>
+        <v>-2.798712827999999</v>
       </c>
       <c r="P98">
-        <v>-12.590946496</v>
+        <v>-12.749691772</v>
       </c>
       <c r="Q98">
-        <v>-7.080946495999997</v>
+        <v>-7.239691771999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.018873534448018</v>
+        <v>1.343231379264024</v>
       </c>
       <c r="T98">
-        <v>16.40741772926021</v>
+        <v>21.87655697234695</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03128360808670616</v>
+        <v>0.03096109666313187</v>
       </c>
       <c r="W98">
-        <v>0.2284233252131547</v>
+        <v>0.2284993734068335</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1737978227039231</v>
+        <v>0.1720060925729548</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2619413335825492</v>
+        <v>0.2638413335825492</v>
       </c>
       <c r="C99">
-        <v>-60.92272109472105</v>
+        <v>-61.87751848626097</v>
       </c>
       <c r="D99">
-        <v>15.47427890527894</v>
+        <v>15.34048151373903</v>
       </c>
       <c r="E99">
-        <v>61.33699999999999</v>
+        <v>62.158</v>
       </c>
       <c r="F99">
-        <v>79.63699999999999</v>
+        <v>80.458</v>
       </c>
       <c r="G99">
         <v>3.24</v>
@@ -9393,37 +9393,37 @@
         <v>3.23</v>
       </c>
       <c r="M99">
-        <v>18.7784046</v>
+        <v>18.9719964</v>
       </c>
       <c r="N99">
-        <v>-15.5484046</v>
+        <v>-15.7419964</v>
       </c>
       <c r="O99">
-        <v>-2.798712827999999</v>
+        <v>-2.833559352</v>
       </c>
       <c r="P99">
-        <v>-12.749691772</v>
+        <v>-12.908437048</v>
       </c>
       <c r="Q99">
-        <v>-7.239691771999999</v>
+        <v>-7.398437048000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.343231379264024</v>
+        <v>1.991947068896035</v>
       </c>
       <c r="T99">
-        <v>21.87655697234695</v>
+        <v>32.81483545852042</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03096109666313187</v>
+        <v>0.0306451671053448</v>
       </c>
       <c r="W99">
-        <v>0.2284993734068335</v>
+        <v>0.2285738695965597</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1720060925729548</v>
+        <v>0.1702509283630267</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2638413335825492</v>
+        <v>0.2657413335825493</v>
       </c>
       <c r="C100">
-        <v>-61.87751848626097</v>
+        <v>-62.83002197025679</v>
       </c>
       <c r="D100">
-        <v>15.34048151373903</v>
+        <v>15.2089780297432</v>
       </c>
       <c r="E100">
-        <v>62.158</v>
+        <v>62.979</v>
       </c>
       <c r="F100">
-        <v>80.458</v>
+        <v>81.279</v>
       </c>
       <c r="G100">
         <v>3.24</v>
@@ -9475,37 +9475,37 @@
         <v>3.23</v>
       </c>
       <c r="M100">
-        <v>18.9719964</v>
+        <v>19.1655882</v>
       </c>
       <c r="N100">
-        <v>-15.7419964</v>
+        <v>-15.9355882</v>
       </c>
       <c r="O100">
-        <v>-2.833559352</v>
+        <v>-2.868405876</v>
       </c>
       <c r="P100">
-        <v>-12.908437048</v>
+        <v>-13.067182324</v>
       </c>
       <c r="Q100">
-        <v>-7.398437048000002</v>
+        <v>-7.557182323999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.991947068896035</v>
+        <v>3.938094137792071</v>
       </c>
       <c r="T100">
-        <v>32.81483545852042</v>
+        <v>65.62967091704084</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0306451671053448</v>
+        <v>0.03033561996286658</v>
       </c>
       <c r="W100">
-        <v>0.2285738695965597</v>
+        <v>0.2286468608127561</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1702509283630267</v>
+        <v>0.1685312220159254</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2657413335825493</v>
-      </c>
-      <c r="C101">
-        <v>-62.83002197025679</v>
-      </c>
-      <c r="D101">
-        <v>15.2089780297432</v>
-      </c>
-      <c r="E101">
-        <v>62.979</v>
-      </c>
-      <c r="F101">
-        <v>81.279</v>
-      </c>
-      <c r="G101">
-        <v>3.24</v>
-      </c>
-      <c r="H101">
-        <v>63.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.74</v>
-      </c>
-      <c r="K101">
-        <v>5.51</v>
-      </c>
-      <c r="L101">
-        <v>3.23</v>
-      </c>
-      <c r="M101">
-        <v>19.1655882</v>
-      </c>
-      <c r="N101">
-        <v>-15.9355882</v>
-      </c>
-      <c r="O101">
-        <v>-2.868405876</v>
-      </c>
-      <c r="P101">
-        <v>-13.067182324</v>
-      </c>
-      <c r="Q101">
-        <v>-7.557182323999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.938094137792071</v>
-      </c>
-      <c r="T101">
-        <v>65.62967091704084</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03033561996286658</v>
-      </c>
-      <c r="W101">
-        <v>0.2286468608127561</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1685312220159254</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
